--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45E031B0-7C6B-4AF7-BD5A-D0461E97922F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C83C3980-87D1-4A39-BFA7-38146952CE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -500,46 +500,46 @@
     <t>efficiency</t>
   </si>
   <si>
-    <t>g_w113757307-220_HRV-w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>g_w162022271-220_HRV-w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w163860997-400_HRV-w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>g_w210745193-220_HRV-w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w273326173-220_HRV-w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w273326173-220_HRV-w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w89817617-220_HRV-w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w89817617-400_HRV-w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>g_w89817617-400_HRV-w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>g_w89818719-400_HRV-w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>g_w89819945-220_HRV-w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>g_w89819945-220_HRV-w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>g_w89820062-400_HRV-w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>g_w96704507-220_HRV-w170366194-220_HRV</t>
+    <t>g_Knin_HRV-KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>g_Kutina_HRV-Sisak_HRV</t>
+  </si>
+  <si>
+    <t>g_Ogulin_HRV-Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>g_Ogulin_HRV-Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>g_Pula_HRV-Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>g_Rijeka_HRV-Knin_HRV</t>
+  </si>
+  <si>
+    <t>g_Rijeka_HRV-VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>g_Sesvete_HRV-Sisak_HRV</t>
+  </si>
+  <si>
+    <t>g_Sesvete_HRV-Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>g_Sibenik_HRV-Split_HRV</t>
+  </si>
+  <si>
+    <t>g_VelikaGorica_HRV-Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>g_Vinkovci_HRV-Osijek_HRV</t>
+  </si>
+  <si>
+    <t>g_Viskovo_HRV-Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>g_Zagreb_HRV-Osijek_HRV</t>
   </si>
   <si>
     <t>~tfm_ins-at</t>
@@ -554,7 +554,7 @@
     <t>lim_type</t>
   </si>
   <si>
-    <t>e_demand_w113757307-220_HRV</t>
+    <t>e_demand_Vinkovci_HRV</t>
   </si>
   <si>
     <t>elc_buildings,elc_transport,elc_roadtransport</t>
@@ -563,187 +563,187 @@
     <t>lo</t>
   </si>
   <si>
-    <t>e_demand_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>e_demand_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>e_demand_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>e_demand_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>e_demand_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>e_demand_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>e_demand_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>e_demand_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>e_demand_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>e_demand_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>e_demand_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>e_demand_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>e_demand_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>e_demand_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>ev_battery_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_PEM_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>H2prd_Elc_ALK_w96704507-220_HRV</t>
+    <t>e_demand_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>e_demand_Knin_HRV</t>
+  </si>
+  <si>
+    <t>e_demand_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>e_demand_Pula_HRV</t>
+  </si>
+  <si>
+    <t>e_demand_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>e_demand_Split_HRV</t>
+  </si>
+  <si>
+    <t>e_demand_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>e_demand_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>e_demand_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>e_demand_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>e_demand_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>e_demand_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>e_demand_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>e_demand_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_Knin_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_Pula_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_Split_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>ev_battery_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Knin_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Pula_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Split_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_PEM_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Knin_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Pula_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Split_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>H2prd_Elc_ALK_Kutina_HRV</t>
   </si>
   <si>
     <t>elc_industry</t>
   </si>
   <si>
-    <t>h_demand_w89818719-400_HRV</t>
+    <t>h_demand_VelikaGorica_HRV</t>
   </si>
   <si>
     <t>het_buildings</t>
@@ -752,19 +752,19 @@
     <t>het_industry</t>
   </si>
   <si>
-    <t>h_demand_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>h_demand_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>h_demand_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>h_demand_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>h_demand_w89819945-220_HRV</t>
+    <t>h_demand_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>h_demand_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>h_demand_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>h_demand_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>h_demand_Sesvete_HRV</t>
   </si>
   <si>
     <t>~tfm_topins</t>
@@ -773,931 +773,931 @@
     <t>io</t>
   </si>
   <si>
-    <t>e_w113757307-220_HRV</t>
+    <t>e_Vinkovci_HRV</t>
   </si>
   <si>
     <t>IN</t>
   </si>
   <si>
-    <t>e_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>e_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>e_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>h_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>h_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>h_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>h_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>h_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>h_w89819945-220_HRV</t>
+    <t>e_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>e_Knin_HRV</t>
+  </si>
+  <si>
+    <t>e_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>e_Pula_HRV</t>
+  </si>
+  <si>
+    <t>e_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>e_Split_HRV</t>
+  </si>
+  <si>
+    <t>e_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>e_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>e_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>e_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>e_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>e_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>e_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>e_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>h_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>h_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>h_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>h_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>h_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>h_Sesvete_HRV</t>
   </si>
   <si>
     <t>region</t>
   </si>
   <si>
-    <t>en_gas_ccgt_w113757307-220_HRV</t>
+    <t>en_gas_ccgt_Vinkovci_HRV</t>
   </si>
   <si>
     <t>OUT</t>
   </si>
   <si>
-    <t>en_gas_turbine_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccgt_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_turbine_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_gas_ccs_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_biomass_chips_ext_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_gas_boiler_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_biomass_chips_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hop_electric_boiler_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_hp_air_10mw_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w113757307-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w162022271-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w163860997-400_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w170366194-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w210745193-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w273326173-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w43337263-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w43337263-400_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w89817617-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w89817617-400_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w89818719-400_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w89819945-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w89820062-400_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w89823918-400_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL_w96704507-220_HRV</t>
-  </si>
-  <si>
-    <t>EN_STG4hbNREL_w96704507-220_HRV</t>
+    <t>en_gas_turbine_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccgt_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_turbine_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_gas_ccs_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_biomass_chips_ext_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_biomass_chips_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_hop_electric_boiler_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_hp_air_10mw_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_chp_gas_cc_ext_ccs_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Knin_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Knin_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Pula_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Pula_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Split_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Split_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>EN_STG4hbNREL_Kutina_HRV</t>
   </si>
   <si>
     <t>ELC</t>
@@ -2405,7 +2405,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{011EEDBF-F2A2-4C3D-8BDD-9EB10427A681}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048C80D6-CF67-4D7D-AE66-709971EEF698}">
   <dimension ref="B2:AG318"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2481,13 +2481,13 @@
         <v>123</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1.7874760000000001</v>
       </c>
       <c r="D4">
-        <v>36.300000000000004</v>
+        <v>110.00000000000001</v>
       </c>
       <c r="E4">
-        <v>0.99802000000000002</v>
+        <v>0.99399999999999999</v>
       </c>
       <c r="H4" t="s">
         <v>141</v>
@@ -2552,13 +2552,13 @@
         <v>124</v>
       </c>
       <c r="C5">
-        <v>1.966224</v>
+        <v>0.49155599999999999</v>
       </c>
       <c r="D5">
-        <v>82.5</v>
+        <v>49.500000000000007</v>
       </c>
       <c r="E5">
-        <v>0.99550000000000005</v>
+        <v>0.99729999999999996</v>
       </c>
       <c r="H5" t="s">
         <v>144</v>
@@ -2620,13 +2620,13 @@
         <v>125</v>
       </c>
       <c r="C6">
-        <v>1.7874760000000001</v>
+        <v>0.49155599999999999</v>
       </c>
       <c r="D6">
-        <v>110.00000000000001</v>
+        <v>129.80000000000001</v>
       </c>
       <c r="E6">
-        <v>0.99399999999999999</v>
+        <v>0.99292000000000002</v>
       </c>
       <c r="H6" t="s">
         <v>145</v>
@@ -2685,13 +2685,13 @@
         <v>126</v>
       </c>
       <c r="C7">
-        <v>0.98311199999999999</v>
+        <v>0.49155599999999999</v>
       </c>
       <c r="D7">
-        <v>51.7</v>
+        <v>159.5</v>
       </c>
       <c r="E7">
-        <v>0.99717999999999996</v>
+        <v>0.99129999999999996</v>
       </c>
       <c r="H7" t="s">
         <v>146</v>
@@ -2735,13 +2735,13 @@
         <v>127</v>
       </c>
       <c r="C8">
-        <v>0.49155599999999999</v>
+        <v>0.98311199999999999</v>
       </c>
       <c r="D8">
-        <v>159.5</v>
+        <v>51.7</v>
       </c>
       <c r="E8">
-        <v>0.99129999999999996</v>
+        <v>0.99717999999999996</v>
       </c>
       <c r="H8" t="s">
         <v>147</v>
@@ -2785,13 +2785,13 @@
         <v>128</v>
       </c>
       <c r="C9">
-        <v>0.49155599999999999</v>
+        <v>1.7874760000000001</v>
       </c>
       <c r="D9">
-        <v>129.80000000000001</v>
+        <v>198.00000000000003</v>
       </c>
       <c r="E9">
-        <v>0.99292000000000002</v>
+        <v>0.98919999999999997</v>
       </c>
       <c r="H9" t="s">
         <v>148</v>
@@ -2835,13 +2835,13 @@
         <v>129</v>
       </c>
       <c r="C10">
-        <v>0.49155599999999999</v>
+        <v>1.7874760000000001</v>
       </c>
       <c r="D10">
-        <v>60.500000000000007</v>
+        <v>140.80000000000001</v>
       </c>
       <c r="E10">
-        <v>0.99670000000000003</v>
+        <v>0.99231999999999998</v>
       </c>
       <c r="H10" t="s">
         <v>149</v>
@@ -2885,13 +2885,13 @@
         <v>130</v>
       </c>
       <c r="C11">
-        <v>1.7874760000000001</v>
+        <v>0.98311199999999999</v>
       </c>
       <c r="D11">
-        <v>198.00000000000003</v>
+        <v>48.400000000000006</v>
       </c>
       <c r="E11">
-        <v>0.98919999999999997</v>
+        <v>0.99736000000000002</v>
       </c>
       <c r="H11" t="s">
         <v>150</v>
@@ -2935,13 +2935,13 @@
         <v>131</v>
       </c>
       <c r="C12">
-        <v>1.7874760000000001</v>
+        <v>7.15</v>
       </c>
       <c r="D12">
-        <v>140.80000000000001</v>
+        <v>26.400000000000002</v>
       </c>
       <c r="E12">
-        <v>0.99231999999999998</v>
+        <v>0.99856</v>
       </c>
       <c r="H12" t="s">
         <v>151</v>
@@ -2985,13 +2985,13 @@
         <v>132</v>
       </c>
       <c r="C13">
-        <v>1.7874760000000001</v>
+        <v>1.966224</v>
       </c>
       <c r="D13">
-        <v>67.100000000000009</v>
+        <v>82.5</v>
       </c>
       <c r="E13">
-        <v>0.99634</v>
+        <v>0.99550000000000005</v>
       </c>
       <c r="H13" t="s">
         <v>152</v>
@@ -3035,13 +3035,13 @@
         <v>133</v>
       </c>
       <c r="C14">
-        <v>0.98311199999999999</v>
+        <v>1.7874760000000001</v>
       </c>
       <c r="D14">
-        <v>48.400000000000006</v>
+        <v>67.100000000000009</v>
       </c>
       <c r="E14">
-        <v>0.99736000000000002</v>
+        <v>0.99634</v>
       </c>
       <c r="H14" t="s">
         <v>153</v>
@@ -3085,13 +3085,13 @@
         <v>134</v>
       </c>
       <c r="C15">
-        <v>7.15</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>26.400000000000002</v>
+        <v>36.300000000000004</v>
       </c>
       <c r="E15">
-        <v>0.99856</v>
+        <v>0.99802000000000002</v>
       </c>
       <c r="H15" t="s">
         <v>154</v>
@@ -3135,13 +3135,13 @@
         <v>135</v>
       </c>
       <c r="C16">
-        <v>1.7874760000000001</v>
+        <v>0.49155599999999999</v>
       </c>
       <c r="D16">
-        <v>254.10000000000002</v>
+        <v>60.500000000000007</v>
       </c>
       <c r="E16">
-        <v>0.98614000000000002</v>
+        <v>0.99670000000000003</v>
       </c>
       <c r="H16" t="s">
         <v>155</v>
@@ -3185,13 +3185,13 @@
         <v>136</v>
       </c>
       <c r="C17">
-        <v>0.49155599999999999</v>
+        <v>1.7874760000000001</v>
       </c>
       <c r="D17">
-        <v>49.500000000000007</v>
+        <v>254.10000000000002</v>
       </c>
       <c r="E17">
-        <v>0.99729999999999996</v>
+        <v>0.98614000000000002</v>
       </c>
       <c r="H17" t="s">
         <v>156</v>
@@ -9688,7 +9688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D006501-9075-493C-B14A-8D6A2DFAF446}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1959BAE8-E268-4BB8-8B6C-0EDB5E57CAAB}">
   <dimension ref="B9:L39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21612,7 +21612,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BE108F9-B0DB-4D36-932B-1AC1C56C1D74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFDB2156-CB31-4E08-8FBB-8FB4E4CF0A8B}">
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C83C3980-87D1-4A39-BFA7-38146952CE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{02B4B42C-65B6-4C74-B9BE-08610E73DC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2405,7 +2405,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048C80D6-CF67-4D7D-AE66-709971EEF698}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A64B530-DE3A-4916-B8B2-5D7F7135BCB4}">
   <dimension ref="B2:AG318"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9688,7 +9688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1959BAE8-E268-4BB8-8B6C-0EDB5E57CAAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3658E24B-FBA1-4F15-8854-135CC6C6D524}">
   <dimension ref="B9:L39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21612,7 +21612,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFDB2156-CB31-4E08-8FBB-8FB4E4CF0A8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2135B8A7-B9FA-4951-A8F1-FAE003F1D437}">
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{02B4B42C-65B6-4C74-B9BE-08610E73DC96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECEA87B0-D138-4E33-BD56-9F6D76E38D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3979" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4159" uniqueCount="604">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -851,36 +851,42 @@
     <t>en_gas_turbine_Vinkovci_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Vinkovci_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_Vinkovci_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Vinkovci_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_Vinkovci_HRV</t>
+    <t>h_Vinkovci_HRV</t>
   </si>
   <si>
     <t>en_chp_biomass_chips_ext_Vinkovci_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_Vinkovci_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_Vinkovci_HRV</t>
   </si>
   <si>
@@ -893,45 +899,48 @@
     <t>en_hp_air_10mw_Vinkovci_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_Vinkovci_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Sibenik_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_Sibenik_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Sibenik_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_Sibenik_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Sibenik_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_Sibenik_HRV</t>
+    <t>h_Sibenik_HRV</t>
   </si>
   <si>
     <t>en_chp_biomass_chips_ext_Sibenik_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_Sibenik_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_Sibenik_HRV</t>
   </si>
   <si>
@@ -944,45 +953,48 @@
     <t>en_hp_air_10mw_Sibenik_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_Sibenik_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Knin_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_Knin_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Knin_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Knin_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_Knin_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_Knin_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Knin_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Knin_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Knin_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Knin_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_Knin_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Knin_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_Knin_HRV</t>
+    <t>h_Knin_HRV</t>
   </si>
   <si>
     <t>en_chp_biomass_chips_ext_Knin_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_Knin_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_Knin_HRV</t>
   </si>
   <si>
@@ -995,45 +1007,45 @@
     <t>en_hp_air_10mw_Knin_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_Knin_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Sisak_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_Sisak_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Sisak_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_Sisak_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_Sisak_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Sisak_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Sisak_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Sisak_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Sisak_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_Sisak_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Sisak_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_Sisak_HRV</t>
-  </si>
-  <si>
     <t>en_chp_biomass_chips_ext_Sisak_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_Sisak_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_Sisak_HRV</t>
   </si>
   <si>
@@ -1046,45 +1058,48 @@
     <t>en_hp_air_10mw_Sisak_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_Sisak_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Pula_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_Pula_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Pula_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Pula_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_Pula_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_Pula_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Pula_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Pula_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Pula_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Pula_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_Pula_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Pula_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_Pula_HRV</t>
+    <t>h_Pula_HRV</t>
   </si>
   <si>
     <t>en_chp_biomass_chips_ext_Pula_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_Pula_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_Pula_HRV</t>
   </si>
   <si>
@@ -1097,45 +1112,48 @@
     <t>en_hp_air_10mw_Pula_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_Pula_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Ogulin_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_Ogulin_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Ogulin_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_Ogulin_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Ogulin_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_Ogulin_HRV</t>
+    <t>h_Ogulin_HRV</t>
   </si>
   <si>
     <t>en_chp_biomass_chips_ext_Ogulin_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_Ogulin_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_Ogulin_HRV</t>
   </si>
   <si>
@@ -1148,45 +1166,48 @@
     <t>en_hp_air_10mw_Ogulin_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_Ogulin_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Split_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_Split_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Split_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Split_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_Split_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_Split_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Split_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Split_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Split_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Split_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_Split_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Split_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_Split_HRV</t>
+    <t>h_Split_HRV</t>
   </si>
   <si>
     <t>en_chp_biomass_chips_ext_Split_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_Split_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_Split_HRV</t>
   </si>
   <si>
@@ -1199,45 +1220,48 @@
     <t>en_hp_air_10mw_Split_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_Split_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_KastelStari_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_KastelStari_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_KastelStari_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_KastelStari_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_KastelStari_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_KastelStari_HRV</t>
+    <t>h_KastelStari_HRV</t>
   </si>
   <si>
     <t>en_chp_biomass_chips_ext_KastelStari_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_KastelStari_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_KastelStari_HRV</t>
   </si>
   <si>
@@ -1250,45 +1274,48 @@
     <t>en_hp_air_10mw_KastelStari_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_KastelStari_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Viskovo_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_Viskovo_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Viskovo_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_Viskovo_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_Viskovo_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Viskovo_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Viskovo_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Viskovo_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Viskovo_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_Viskovo_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Viskovo_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_Viskovo_HRV</t>
+    <t>h_Viskovo_HRV</t>
   </si>
   <si>
     <t>en_chp_biomass_chips_ext_Viskovo_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_Viskovo_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_Viskovo_HRV</t>
   </si>
   <si>
@@ -1301,45 +1328,48 @@
     <t>en_hp_air_10mw_Viskovo_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_Viskovo_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Rijeka_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_Rijeka_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Rijeka_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_Rijeka_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Rijeka_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_Rijeka_HRV</t>
+    <t>h_Rijeka_HRV</t>
   </si>
   <si>
     <t>en_chp_biomass_chips_ext_Rijeka_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_Rijeka_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_Rijeka_HRV</t>
   </si>
   <si>
@@ -1352,45 +1382,45 @@
     <t>en_hp_air_10mw_Rijeka_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_Rijeka_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_VelikaGorica_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_VelikaGorica_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_VelikaGorica_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_VelikaGorica_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_VelikaGorica_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_VelikaGorica_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_VelikaGorica_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_VelikaGorica_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_VelikaGorica_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_VelikaGorica_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_VelikaGorica_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_VelikaGorica_HRV</t>
-  </si>
-  <si>
     <t>en_chp_biomass_chips_ext_VelikaGorica_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_VelikaGorica_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_VelikaGorica_HRV</t>
   </si>
   <si>
@@ -1403,45 +1433,45 @@
     <t>en_hp_air_10mw_VelikaGorica_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_VelikaGorica_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Sesvete_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_Sesvete_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Sesvete_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_Sesvete_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_Sesvete_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Sesvete_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Sesvete_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Sesvete_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Sesvete_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_Sesvete_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Sesvete_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_Sesvete_HRV</t>
-  </si>
-  <si>
     <t>en_chp_biomass_chips_ext_Sesvete_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_Sesvete_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_Sesvete_HRV</t>
   </si>
   <si>
@@ -1454,45 +1484,45 @@
     <t>en_hp_air_10mw_Sesvete_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_Sesvete_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Zagreb_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_Zagreb_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Zagreb_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_Zagreb_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Zagreb_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_Zagreb_HRV</t>
-  </si>
-  <si>
     <t>en_chp_biomass_chips_ext_Zagreb_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_Zagreb_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_Zagreb_HRV</t>
   </si>
   <si>
@@ -1505,45 +1535,45 @@
     <t>en_hp_air_10mw_Zagreb_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_Zagreb_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Osijek_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_Osijek_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Osijek_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_Osijek_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_Osijek_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Osijek_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Osijek_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Osijek_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Osijek_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_Osijek_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Osijek_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_Osijek_HRV</t>
-  </si>
-  <si>
     <t>en_chp_biomass_chips_ext_Osijek_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_Osijek_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_Osijek_HRV</t>
   </si>
   <si>
@@ -1556,45 +1586,45 @@
     <t>en_hp_air_10mw_Osijek_HRV</t>
   </si>
   <si>
-    <t>en_chp_gas_cc_ext_ccs_Osijek_HRV</t>
-  </si>
-  <si>
     <t>en_gas_ccgt_Kutina_HRV</t>
   </si>
   <si>
     <t>en_gas_turbine_Kutina_HRV</t>
   </si>
   <si>
+    <t>en_gas_ccs_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_subcritical_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_supercritical_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_ultrasupercritical_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_coal_igcc_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_nuclear_smr_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>en_biomass_Kutina_HRV</t>
+  </si>
+  <si>
     <t>en_chp_gas_cc_ext_Kutina_HRV</t>
   </si>
   <si>
-    <t>en_gas_ccs_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_subcritical_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_supercritical_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_ultrasupercritical_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>en_coal_igcc_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>en_nuclear_smr_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>en_biomass_Kutina_HRV</t>
-  </si>
-  <si>
     <t>en_chp_biomass_chips_ext_Kutina_HRV</t>
   </si>
   <si>
+    <t>en_chp_gas_cc_ext_ccs_Kutina_HRV</t>
+  </si>
+  <si>
     <t>en_hop_gas_boiler_Kutina_HRV</t>
   </si>
   <si>
@@ -1605,9 +1635,6 @@
   </si>
   <si>
     <t>en_hp_air_10mw_Kutina_HRV</t>
-  </si>
-  <si>
-    <t>en_chp_gas_cc_ext_ccs_Kutina_HRV</t>
   </si>
   <si>
     <t>EN_STG8hbNREL_Vinkovci_HRV</t>
@@ -2405,8 +2432,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A64B530-DE3A-4916-B8B2-5D7F7135BCB4}">
-  <dimension ref="B2:AG318"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F258A61-617F-40B5-90A4-0CC5474F8BD2}">
+  <dimension ref="B2:AG363"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="2" spans="2:33" x14ac:dyDescent="0.45">
@@ -2529,22 +2556,22 @@
         <v>138</v>
       </c>
       <c r="AB4" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="AC4" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="AD4" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="AE4" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="AF4" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="AG4" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.45">
@@ -2597,10 +2624,10 @@
         <v>238</v>
       </c>
       <c r="AA5" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="AB5" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="AC5">
         <v>2</v>
@@ -2609,10 +2636,10 @@
         <v>0</v>
       </c>
       <c r="AF5" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="AG5" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.45">
@@ -2665,10 +2692,10 @@
         <v>238</v>
       </c>
       <c r="AA6" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="AB6" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="AD6">
         <v>2</v>
@@ -2677,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="AF6" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.45">
@@ -3121,10 +3148,10 @@
         <v>119</v>
       </c>
       <c r="V15" t="s">
+        <v>248</v>
+      </c>
+      <c r="W15" t="s">
         <v>249</v>
-      </c>
-      <c r="W15" t="s">
-        <v>214</v>
       </c>
       <c r="X15" t="s">
         <v>238</v>
@@ -3221,10 +3248,10 @@
         <v>119</v>
       </c>
       <c r="V17" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="W17" t="s">
-        <v>214</v>
+        <v>249</v>
       </c>
       <c r="X17" t="s">
         <v>238</v>
@@ -3259,7 +3286,7 @@
         <v>119</v>
       </c>
       <c r="V18" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="W18" t="s">
         <v>214</v>
@@ -3297,10 +3324,10 @@
         <v>119</v>
       </c>
       <c r="V19" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="W19" t="s">
-        <v>214</v>
+        <v>249</v>
       </c>
       <c r="X19" t="s">
         <v>238</v>
@@ -3335,10 +3362,10 @@
         <v>119</v>
       </c>
       <c r="V20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="W20" t="s">
-        <v>214</v>
+        <v>249</v>
       </c>
       <c r="X20" t="s">
         <v>238</v>
@@ -3373,10 +3400,10 @@
         <v>119</v>
       </c>
       <c r="V21" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="W21" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="X21" t="s">
         <v>238</v>
@@ -3411,10 +3438,10 @@
         <v>119</v>
       </c>
       <c r="V22" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="W22" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="X22" t="s">
         <v>238</v>
@@ -3449,10 +3476,10 @@
         <v>119</v>
       </c>
       <c r="V23" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="W23" t="s">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="X23" t="s">
         <v>238</v>
@@ -3487,7 +3514,7 @@
         <v>119</v>
       </c>
       <c r="V24" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="W24" t="s">
         <v>216</v>
@@ -3525,7 +3552,7 @@
         <v>119</v>
       </c>
       <c r="V25" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W25" t="s">
         <v>216</v>
@@ -3563,7 +3590,7 @@
         <v>119</v>
       </c>
       <c r="V26" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="W26" t="s">
         <v>216</v>
@@ -3601,7 +3628,7 @@
         <v>119</v>
       </c>
       <c r="V27" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="W27" t="s">
         <v>216</v>
@@ -3639,7 +3666,7 @@
         <v>119</v>
       </c>
       <c r="V28" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="W28" t="s">
         <v>216</v>
@@ -3677,7 +3704,7 @@
         <v>119</v>
       </c>
       <c r="V29" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="W29" t="s">
         <v>216</v>
@@ -3715,7 +3742,7 @@
         <v>119</v>
       </c>
       <c r="V30" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="W30" t="s">
         <v>216</v>
@@ -3753,7 +3780,7 @@
         <v>119</v>
       </c>
       <c r="V31" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="W31" t="s">
         <v>216</v>
@@ -3791,7 +3818,7 @@
         <v>119</v>
       </c>
       <c r="V32" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="W32" t="s">
         <v>216</v>
@@ -3829,7 +3856,7 @@
         <v>119</v>
       </c>
       <c r="V33" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="W33" t="s">
         <v>216</v>
@@ -3867,7 +3894,7 @@
         <v>119</v>
       </c>
       <c r="V34" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="W34" t="s">
         <v>216</v>
@@ -3905,10 +3932,10 @@
         <v>119</v>
       </c>
       <c r="V35" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="W35" t="s">
-        <v>216</v>
+        <v>267</v>
       </c>
       <c r="X35" t="s">
         <v>238</v>
@@ -3943,7 +3970,7 @@
         <v>119</v>
       </c>
       <c r="V36" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="W36" t="s">
         <v>216</v>
@@ -3981,10 +4008,10 @@
         <v>119</v>
       </c>
       <c r="V37" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="W37" t="s">
-        <v>216</v>
+        <v>267</v>
       </c>
       <c r="X37" t="s">
         <v>238</v>
@@ -4019,10 +4046,10 @@
         <v>119</v>
       </c>
       <c r="V38" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="W38" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="X38" t="s">
         <v>238</v>
@@ -4057,10 +4084,10 @@
         <v>119</v>
       </c>
       <c r="V39" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="W39" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="X39" t="s">
         <v>238</v>
@@ -4095,10 +4122,10 @@
         <v>119</v>
       </c>
       <c r="V40" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="W40" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="X40" t="s">
         <v>238</v>
@@ -4133,10 +4160,10 @@
         <v>119</v>
       </c>
       <c r="V41" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="W41" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="X41" t="s">
         <v>238</v>
@@ -4171,10 +4198,10 @@
         <v>119</v>
       </c>
       <c r="V42" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="W42" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="X42" t="s">
         <v>238</v>
@@ -4209,10 +4236,10 @@
         <v>119</v>
       </c>
       <c r="V43" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="W43" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="X43" t="s">
         <v>238</v>
@@ -4247,7 +4274,7 @@
         <v>119</v>
       </c>
       <c r="V44" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="W44" t="s">
         <v>217</v>
@@ -4285,7 +4312,7 @@
         <v>119</v>
       </c>
       <c r="V45" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="W45" t="s">
         <v>217</v>
@@ -4323,7 +4350,7 @@
         <v>119</v>
       </c>
       <c r="V46" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="W46" t="s">
         <v>217</v>
@@ -4361,7 +4388,7 @@
         <v>119</v>
       </c>
       <c r="V47" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="W47" t="s">
         <v>217</v>
@@ -4399,7 +4426,7 @@
         <v>119</v>
       </c>
       <c r="V48" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="W48" t="s">
         <v>217</v>
@@ -4437,7 +4464,7 @@
         <v>119</v>
       </c>
       <c r="V49" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="W49" t="s">
         <v>217</v>
@@ -4475,7 +4502,7 @@
         <v>119</v>
       </c>
       <c r="V50" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="W50" t="s">
         <v>217</v>
@@ -4513,7 +4540,7 @@
         <v>119</v>
       </c>
       <c r="V51" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="W51" t="s">
         <v>217</v>
@@ -4551,7 +4578,7 @@
         <v>119</v>
       </c>
       <c r="V52" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="W52" t="s">
         <v>217</v>
@@ -4589,7 +4616,7 @@
         <v>119</v>
       </c>
       <c r="V53" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="W53" t="s">
         <v>217</v>
@@ -4627,7 +4654,7 @@
         <v>119</v>
       </c>
       <c r="V54" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="W54" t="s">
         <v>217</v>
@@ -4665,10 +4692,10 @@
         <v>119</v>
       </c>
       <c r="V55" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="W55" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="X55" t="s">
         <v>238</v>
@@ -4703,10 +4730,10 @@
         <v>119</v>
       </c>
       <c r="V56" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="W56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="X56" t="s">
         <v>238</v>
@@ -4741,10 +4768,10 @@
         <v>119</v>
       </c>
       <c r="V57" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="W57" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="X57" t="s">
         <v>238</v>
@@ -4779,10 +4806,10 @@
         <v>119</v>
       </c>
       <c r="V58" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="W58" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="X58" t="s">
         <v>238</v>
@@ -4817,10 +4844,10 @@
         <v>119</v>
       </c>
       <c r="V59" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="W59" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="X59" t="s">
         <v>238</v>
@@ -4855,10 +4882,10 @@
         <v>119</v>
       </c>
       <c r="V60" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="W60" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="X60" t="s">
         <v>238</v>
@@ -4893,10 +4920,10 @@
         <v>119</v>
       </c>
       <c r="V61" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="W61" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="X61" t="s">
         <v>238</v>
@@ -4931,10 +4958,10 @@
         <v>119</v>
       </c>
       <c r="V62" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="W62" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="X62" t="s">
         <v>238</v>
@@ -4969,10 +4996,10 @@
         <v>119</v>
       </c>
       <c r="V63" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="W63" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="X63" t="s">
         <v>238</v>
@@ -5007,7 +5034,7 @@
         <v>119</v>
       </c>
       <c r="V64" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="W64" t="s">
         <v>218</v>
@@ -5045,7 +5072,7 @@
         <v>119</v>
       </c>
       <c r="V65" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="W65" t="s">
         <v>218</v>
@@ -5083,7 +5110,7 @@
         <v>119</v>
       </c>
       <c r="V66" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="W66" t="s">
         <v>218</v>
@@ -5121,7 +5148,7 @@
         <v>119</v>
       </c>
       <c r="V67" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="W67" t="s">
         <v>218</v>
@@ -5159,7 +5186,7 @@
         <v>119</v>
       </c>
       <c r="V68" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="W68" t="s">
         <v>218</v>
@@ -5197,7 +5224,7 @@
         <v>119</v>
       </c>
       <c r="V69" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="W69" t="s">
         <v>218</v>
@@ -5226,7 +5253,7 @@
         <v>119</v>
       </c>
       <c r="V70" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="W70" t="s">
         <v>218</v>
@@ -5255,7 +5282,7 @@
         <v>119</v>
       </c>
       <c r="V71" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="W71" t="s">
         <v>218</v>
@@ -5284,10 +5311,10 @@
         <v>119</v>
       </c>
       <c r="V72" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="W72" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="X72" t="s">
         <v>238</v>
@@ -5313,10 +5340,10 @@
         <v>119</v>
       </c>
       <c r="V73" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="W73" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="X73" t="s">
         <v>238</v>
@@ -5342,10 +5369,10 @@
         <v>119</v>
       </c>
       <c r="V74" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="W74" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="X74" t="s">
         <v>238</v>
@@ -5371,10 +5398,10 @@
         <v>119</v>
       </c>
       <c r="V75" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="W75" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="X75" t="s">
         <v>238</v>
@@ -5400,10 +5427,10 @@
         <v>119</v>
       </c>
       <c r="V76" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="W76" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="X76" t="s">
         <v>238</v>
@@ -5429,10 +5456,10 @@
         <v>119</v>
       </c>
       <c r="V77" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="W77" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="X77" t="s">
         <v>238</v>
@@ -5458,10 +5485,10 @@
         <v>119</v>
       </c>
       <c r="V78" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="W78" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="X78" t="s">
         <v>238</v>
@@ -5487,10 +5514,10 @@
         <v>119</v>
       </c>
       <c r="V79" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="W79" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="X79" t="s">
         <v>238</v>
@@ -5516,10 +5543,10 @@
         <v>119</v>
       </c>
       <c r="V80" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="W80" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="X80" t="s">
         <v>238</v>
@@ -5545,10 +5572,10 @@
         <v>119</v>
       </c>
       <c r="V81" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="W81" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="X81" t="s">
         <v>238</v>
@@ -5574,10 +5601,10 @@
         <v>119</v>
       </c>
       <c r="V82" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="W82" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="X82" t="s">
         <v>238</v>
@@ -5603,10 +5630,10 @@
         <v>119</v>
       </c>
       <c r="V83" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="W83" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="X83" t="s">
         <v>238</v>
@@ -5632,7 +5659,7 @@
         <v>119</v>
       </c>
       <c r="V84" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="W84" t="s">
         <v>219</v>
@@ -5661,7 +5688,7 @@
         <v>119</v>
       </c>
       <c r="V85" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="W85" t="s">
         <v>219</v>
@@ -5690,7 +5717,7 @@
         <v>119</v>
       </c>
       <c r="V86" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="W86" t="s">
         <v>219</v>
@@ -5719,7 +5746,7 @@
         <v>119</v>
       </c>
       <c r="V87" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="W87" t="s">
         <v>219</v>
@@ -5748,7 +5775,7 @@
         <v>119</v>
       </c>
       <c r="V88" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="W88" t="s">
         <v>219</v>
@@ -5777,10 +5804,10 @@
         <v>119</v>
       </c>
       <c r="V89" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="W89" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X89" t="s">
         <v>238</v>
@@ -5806,10 +5833,10 @@
         <v>119</v>
       </c>
       <c r="V90" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="W90" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X90" t="s">
         <v>238</v>
@@ -5835,10 +5862,10 @@
         <v>119</v>
       </c>
       <c r="V91" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="W91" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X91" t="s">
         <v>238</v>
@@ -5864,10 +5891,10 @@
         <v>119</v>
       </c>
       <c r="V92" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="W92" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X92" t="s">
         <v>238</v>
@@ -5893,10 +5920,10 @@
         <v>119</v>
       </c>
       <c r="V93" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="W93" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X93" t="s">
         <v>238</v>
@@ -5922,10 +5949,10 @@
         <v>119</v>
       </c>
       <c r="V94" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="W94" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X94" t="s">
         <v>238</v>
@@ -5951,10 +5978,10 @@
         <v>119</v>
       </c>
       <c r="V95" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="W95" t="s">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="X95" t="s">
         <v>238</v>
@@ -5980,10 +6007,10 @@
         <v>119</v>
       </c>
       <c r="V96" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="W96" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X96" t="s">
         <v>238</v>
@@ -6009,10 +6036,10 @@
         <v>119</v>
       </c>
       <c r="V97" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="W97" t="s">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="X97" t="s">
         <v>238</v>
@@ -6038,10 +6065,10 @@
         <v>119</v>
       </c>
       <c r="V98" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="W98" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="X98" t="s">
         <v>238</v>
@@ -6067,10 +6094,10 @@
         <v>119</v>
       </c>
       <c r="V99" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="W99" t="s">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="X99" t="s">
         <v>238</v>
@@ -6096,10 +6123,10 @@
         <v>119</v>
       </c>
       <c r="V100" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="W100" t="s">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="X100" t="s">
         <v>238</v>
@@ -6125,10 +6152,10 @@
         <v>119</v>
       </c>
       <c r="V101" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="W101" t="s">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="X101" t="s">
         <v>238</v>
@@ -6154,10 +6181,10 @@
         <v>119</v>
       </c>
       <c r="V102" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="W102" t="s">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="X102" t="s">
         <v>238</v>
@@ -6183,10 +6210,10 @@
         <v>119</v>
       </c>
       <c r="V103" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="W103" t="s">
-        <v>220</v>
+        <v>320</v>
       </c>
       <c r="X103" t="s">
         <v>238</v>
@@ -6212,7 +6239,7 @@
         <v>119</v>
       </c>
       <c r="V104" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="W104" t="s">
         <v>220</v>
@@ -6241,7 +6268,7 @@
         <v>119</v>
       </c>
       <c r="V105" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="W105" t="s">
         <v>220</v>
@@ -6270,10 +6297,10 @@
         <v>119</v>
       </c>
       <c r="V106" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="W106" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X106" t="s">
         <v>238</v>
@@ -6299,10 +6326,10 @@
         <v>119</v>
       </c>
       <c r="V107" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="W107" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X107" t="s">
         <v>238</v>
@@ -6328,10 +6355,10 @@
         <v>119</v>
       </c>
       <c r="V108" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="W108" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X108" t="s">
         <v>238</v>
@@ -6357,10 +6384,10 @@
         <v>119</v>
       </c>
       <c r="V109" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="W109" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X109" t="s">
         <v>238</v>
@@ -6386,10 +6413,10 @@
         <v>119</v>
       </c>
       <c r="V110" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="W110" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X110" t="s">
         <v>238</v>
@@ -6415,10 +6442,10 @@
         <v>119</v>
       </c>
       <c r="V111" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="W111" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X111" t="s">
         <v>238</v>
@@ -6444,10 +6471,10 @@
         <v>119</v>
       </c>
       <c r="V112" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="W112" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X112" t="s">
         <v>238</v>
@@ -6473,10 +6500,10 @@
         <v>119</v>
       </c>
       <c r="V113" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="W113" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X113" t="s">
         <v>238</v>
@@ -6502,10 +6529,10 @@
         <v>119</v>
       </c>
       <c r="V114" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="W114" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X114" t="s">
         <v>238</v>
@@ -6531,10 +6558,10 @@
         <v>119</v>
       </c>
       <c r="V115" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="W115" t="s">
-        <v>221</v>
+        <v>338</v>
       </c>
       <c r="X115" t="s">
         <v>238</v>
@@ -6560,10 +6587,10 @@
         <v>119</v>
       </c>
       <c r="V116" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="W116" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X116" t="s">
         <v>238</v>
@@ -6589,10 +6616,10 @@
         <v>119</v>
       </c>
       <c r="V117" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="W117" t="s">
-        <v>221</v>
+        <v>338</v>
       </c>
       <c r="X117" t="s">
         <v>238</v>
@@ -6618,10 +6645,10 @@
         <v>119</v>
       </c>
       <c r="V118" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="W118" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="X118" t="s">
         <v>238</v>
@@ -6647,10 +6674,10 @@
         <v>119</v>
       </c>
       <c r="V119" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="W119" t="s">
-        <v>221</v>
+        <v>338</v>
       </c>
       <c r="X119" t="s">
         <v>238</v>
@@ -6676,10 +6703,10 @@
         <v>119</v>
       </c>
       <c r="V120" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="W120" t="s">
-        <v>221</v>
+        <v>338</v>
       </c>
       <c r="X120" t="s">
         <v>238</v>
@@ -6705,10 +6732,10 @@
         <v>119</v>
       </c>
       <c r="V121" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="W121" t="s">
-        <v>221</v>
+        <v>338</v>
       </c>
       <c r="X121" t="s">
         <v>238</v>
@@ -6734,10 +6761,10 @@
         <v>119</v>
       </c>
       <c r="V122" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="W122" t="s">
-        <v>221</v>
+        <v>338</v>
       </c>
       <c r="X122" t="s">
         <v>238</v>
@@ -6763,10 +6790,10 @@
         <v>119</v>
       </c>
       <c r="V123" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="W123" t="s">
-        <v>222</v>
+        <v>338</v>
       </c>
       <c r="X123" t="s">
         <v>238</v>
@@ -6792,10 +6819,10 @@
         <v>119</v>
       </c>
       <c r="V124" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="W124" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X124" t="s">
         <v>238</v>
@@ -6821,10 +6848,10 @@
         <v>119</v>
       </c>
       <c r="V125" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="W125" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X125" t="s">
         <v>238</v>
@@ -6850,10 +6877,10 @@
         <v>119</v>
       </c>
       <c r="V126" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="W126" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X126" t="s">
         <v>238</v>
@@ -6879,10 +6906,10 @@
         <v>119</v>
       </c>
       <c r="V127" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="W127" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X127" t="s">
         <v>238</v>
@@ -6908,10 +6935,10 @@
         <v>119</v>
       </c>
       <c r="V128" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="W128" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X128" t="s">
         <v>238</v>
@@ -6937,10 +6964,10 @@
         <v>119</v>
       </c>
       <c r="V129" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="W129" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X129" t="s">
         <v>238</v>
@@ -6966,10 +6993,10 @@
         <v>119</v>
       </c>
       <c r="V130" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="W130" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X130" t="s">
         <v>238</v>
@@ -6995,10 +7022,10 @@
         <v>119</v>
       </c>
       <c r="V131" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="W131" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X131" t="s">
         <v>238</v>
@@ -7024,10 +7051,10 @@
         <v>119</v>
       </c>
       <c r="V132" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="W132" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X132" t="s">
         <v>238</v>
@@ -7053,10 +7080,10 @@
         <v>119</v>
       </c>
       <c r="V133" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="W133" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X133" t="s">
         <v>238</v>
@@ -7082,10 +7109,10 @@
         <v>119</v>
       </c>
       <c r="V134" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="W134" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X134" t="s">
         <v>238</v>
@@ -7111,10 +7138,10 @@
         <v>119</v>
       </c>
       <c r="V135" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="W135" t="s">
-        <v>222</v>
+        <v>356</v>
       </c>
       <c r="X135" t="s">
         <v>238</v>
@@ -7125,10 +7152,10 @@
         <v>119</v>
       </c>
       <c r="V136" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="W136" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X136" t="s">
         <v>238</v>
@@ -7139,10 +7166,10 @@
         <v>119</v>
       </c>
       <c r="V137" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="W137" t="s">
-        <v>222</v>
+        <v>356</v>
       </c>
       <c r="X137" t="s">
         <v>238</v>
@@ -7153,10 +7180,10 @@
         <v>119</v>
       </c>
       <c r="V138" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="W138" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="X138" t="s">
         <v>238</v>
@@ -7167,10 +7194,10 @@
         <v>119</v>
       </c>
       <c r="V139" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="W139" t="s">
-        <v>222</v>
+        <v>356</v>
       </c>
       <c r="X139" t="s">
         <v>238</v>
@@ -7181,10 +7208,10 @@
         <v>119</v>
       </c>
       <c r="V140" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="W140" t="s">
-        <v>223</v>
+        <v>356</v>
       </c>
       <c r="X140" t="s">
         <v>238</v>
@@ -7195,10 +7222,10 @@
         <v>119</v>
       </c>
       <c r="V141" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="W141" t="s">
-        <v>223</v>
+        <v>356</v>
       </c>
       <c r="X141" t="s">
         <v>238</v>
@@ -7209,10 +7236,10 @@
         <v>119</v>
       </c>
       <c r="V142" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="W142" t="s">
-        <v>223</v>
+        <v>356</v>
       </c>
       <c r="X142" t="s">
         <v>238</v>
@@ -7223,10 +7250,10 @@
         <v>119</v>
       </c>
       <c r="V143" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="W143" t="s">
-        <v>223</v>
+        <v>356</v>
       </c>
       <c r="X143" t="s">
         <v>238</v>
@@ -7237,10 +7264,10 @@
         <v>119</v>
       </c>
       <c r="V144" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="W144" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X144" t="s">
         <v>238</v>
@@ -7251,10 +7278,10 @@
         <v>119</v>
       </c>
       <c r="V145" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="W145" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X145" t="s">
         <v>238</v>
@@ -7265,10 +7292,10 @@
         <v>119</v>
       </c>
       <c r="V146" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="W146" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X146" t="s">
         <v>238</v>
@@ -7279,10 +7306,10 @@
         <v>119</v>
       </c>
       <c r="V147" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="W147" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X147" t="s">
         <v>238</v>
@@ -7293,10 +7320,10 @@
         <v>119</v>
       </c>
       <c r="V148" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="W148" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X148" t="s">
         <v>238</v>
@@ -7307,10 +7334,10 @@
         <v>119</v>
       </c>
       <c r="V149" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="W149" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X149" t="s">
         <v>238</v>
@@ -7321,10 +7348,10 @@
         <v>119</v>
       </c>
       <c r="V150" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="W150" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X150" t="s">
         <v>238</v>
@@ -7335,10 +7362,10 @@
         <v>119</v>
       </c>
       <c r="V151" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="W151" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X151" t="s">
         <v>238</v>
@@ -7349,10 +7376,10 @@
         <v>119</v>
       </c>
       <c r="V152" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="W152" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X152" t="s">
         <v>238</v>
@@ -7363,10 +7390,10 @@
         <v>119</v>
       </c>
       <c r="V153" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="W153" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X153" t="s">
         <v>238</v>
@@ -7377,10 +7404,10 @@
         <v>119</v>
       </c>
       <c r="V154" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="W154" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X154" t="s">
         <v>238</v>
@@ -7391,10 +7418,10 @@
         <v>119</v>
       </c>
       <c r="V155" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="W155" t="s">
-        <v>223</v>
+        <v>374</v>
       </c>
       <c r="X155" t="s">
         <v>238</v>
@@ -7405,10 +7432,10 @@
         <v>119</v>
       </c>
       <c r="V156" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="W156" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="X156" t="s">
         <v>238</v>
@@ -7419,10 +7446,10 @@
         <v>119</v>
       </c>
       <c r="V157" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="W157" t="s">
-        <v>224</v>
+        <v>374</v>
       </c>
       <c r="X157" t="s">
         <v>238</v>
@@ -7433,10 +7460,10 @@
         <v>119</v>
       </c>
       <c r="V158" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="W158" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="X158" t="s">
         <v>238</v>
@@ -7447,10 +7474,10 @@
         <v>119</v>
       </c>
       <c r="V159" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="W159" t="s">
-        <v>224</v>
+        <v>374</v>
       </c>
       <c r="X159" t="s">
         <v>238</v>
@@ -7461,10 +7488,10 @@
         <v>119</v>
       </c>
       <c r="V160" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="W160" t="s">
-        <v>224</v>
+        <v>374</v>
       </c>
       <c r="X160" t="s">
         <v>238</v>
@@ -7475,10 +7502,10 @@
         <v>119</v>
       </c>
       <c r="V161" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="W161" t="s">
-        <v>224</v>
+        <v>374</v>
       </c>
       <c r="X161" t="s">
         <v>238</v>
@@ -7489,10 +7516,10 @@
         <v>119</v>
       </c>
       <c r="V162" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="W162" t="s">
-        <v>224</v>
+        <v>374</v>
       </c>
       <c r="X162" t="s">
         <v>238</v>
@@ -7503,10 +7530,10 @@
         <v>119</v>
       </c>
       <c r="V163" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="W163" t="s">
-        <v>224</v>
+        <v>374</v>
       </c>
       <c r="X163" t="s">
         <v>238</v>
@@ -7517,10 +7544,10 @@
         <v>119</v>
       </c>
       <c r="V164" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="W164" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X164" t="s">
         <v>238</v>
@@ -7531,10 +7558,10 @@
         <v>119</v>
       </c>
       <c r="V165" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="W165" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X165" t="s">
         <v>238</v>
@@ -7545,10 +7572,10 @@
         <v>119</v>
       </c>
       <c r="V166" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="W166" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X166" t="s">
         <v>238</v>
@@ -7559,10 +7586,10 @@
         <v>119</v>
       </c>
       <c r="V167" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="W167" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X167" t="s">
         <v>238</v>
@@ -7573,10 +7600,10 @@
         <v>119</v>
       </c>
       <c r="V168" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="W168" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X168" t="s">
         <v>238</v>
@@ -7587,10 +7614,10 @@
         <v>119</v>
       </c>
       <c r="V169" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="W169" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X169" t="s">
         <v>238</v>
@@ -7601,10 +7628,10 @@
         <v>119</v>
       </c>
       <c r="V170" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="W170" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X170" t="s">
         <v>238</v>
@@ -7615,10 +7642,10 @@
         <v>119</v>
       </c>
       <c r="V171" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="W171" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X171" t="s">
         <v>238</v>
@@ -7629,10 +7656,10 @@
         <v>119</v>
       </c>
       <c r="V172" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="W172" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X172" t="s">
         <v>238</v>
@@ -7643,10 +7670,10 @@
         <v>119</v>
       </c>
       <c r="V173" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="W173" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="X173" t="s">
         <v>238</v>
@@ -7657,10 +7684,10 @@
         <v>119</v>
       </c>
       <c r="V174" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="W174" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="X174" t="s">
         <v>238</v>
@@ -7671,10 +7698,10 @@
         <v>119</v>
       </c>
       <c r="V175" t="s">
-        <v>409</v>
+        <v>391</v>
       </c>
       <c r="W175" t="s">
-        <v>225</v>
+        <v>392</v>
       </c>
       <c r="X175" t="s">
         <v>238</v>
@@ -7685,10 +7712,10 @@
         <v>119</v>
       </c>
       <c r="V176" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="W176" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="X176" t="s">
         <v>238</v>
@@ -7699,10 +7726,10 @@
         <v>119</v>
       </c>
       <c r="V177" t="s">
-        <v>411</v>
+        <v>393</v>
       </c>
       <c r="W177" t="s">
-        <v>225</v>
+        <v>392</v>
       </c>
       <c r="X177" t="s">
         <v>238</v>
@@ -7713,10 +7740,10 @@
         <v>119</v>
       </c>
       <c r="V178" t="s">
-        <v>412</v>
+        <v>394</v>
       </c>
       <c r="W178" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="X178" t="s">
         <v>238</v>
@@ -7727,10 +7754,10 @@
         <v>119</v>
       </c>
       <c r="V179" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="W179" t="s">
-        <v>225</v>
+        <v>392</v>
       </c>
       <c r="X179" t="s">
         <v>238</v>
@@ -7741,10 +7768,10 @@
         <v>119</v>
       </c>
       <c r="V180" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="W180" t="s">
-        <v>225</v>
+        <v>392</v>
       </c>
       <c r="X180" t="s">
         <v>238</v>
@@ -7755,10 +7782,10 @@
         <v>119</v>
       </c>
       <c r="V181" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="W181" t="s">
-        <v>225</v>
+        <v>392</v>
       </c>
       <c r="X181" t="s">
         <v>238</v>
@@ -7769,10 +7796,10 @@
         <v>119</v>
       </c>
       <c r="V182" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="W182" t="s">
-        <v>225</v>
+        <v>392</v>
       </c>
       <c r="X182" t="s">
         <v>238</v>
@@ -7783,10 +7810,10 @@
         <v>119</v>
       </c>
       <c r="V183" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="W183" t="s">
-        <v>225</v>
+        <v>392</v>
       </c>
       <c r="X183" t="s">
         <v>238</v>
@@ -7797,10 +7824,10 @@
         <v>119</v>
       </c>
       <c r="V184" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="W184" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X184" t="s">
         <v>238</v>
@@ -7811,10 +7838,10 @@
         <v>119</v>
       </c>
       <c r="V185" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="W185" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X185" t="s">
         <v>238</v>
@@ -7825,10 +7852,10 @@
         <v>119</v>
       </c>
       <c r="V186" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="W186" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X186" t="s">
         <v>238</v>
@@ -7839,10 +7866,10 @@
         <v>119</v>
       </c>
       <c r="V187" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="W187" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X187" t="s">
         <v>238</v>
@@ -7853,10 +7880,10 @@
         <v>119</v>
       </c>
       <c r="V188" t="s">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="W188" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X188" t="s">
         <v>238</v>
@@ -7867,10 +7894,10 @@
         <v>119</v>
       </c>
       <c r="V189" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="W189" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X189" t="s">
         <v>238</v>
@@ -7881,10 +7908,10 @@
         <v>119</v>
       </c>
       <c r="V190" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="W190" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="X190" t="s">
         <v>238</v>
@@ -7895,10 +7922,10 @@
         <v>119</v>
       </c>
       <c r="V191" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="W191" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X191" t="s">
         <v>238</v>
@@ -7909,10 +7936,10 @@
         <v>119</v>
       </c>
       <c r="V192" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="W192" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X192" t="s">
         <v>238</v>
@@ -7923,10 +7950,10 @@
         <v>119</v>
       </c>
       <c r="V193" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="W193" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X193" t="s">
         <v>238</v>
@@ -7937,10 +7964,10 @@
         <v>119</v>
       </c>
       <c r="V194" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="W194" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X194" t="s">
         <v>238</v>
@@ -7951,10 +7978,10 @@
         <v>119</v>
       </c>
       <c r="V195" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="W195" t="s">
-        <v>226</v>
+        <v>410</v>
       </c>
       <c r="X195" t="s">
         <v>238</v>
@@ -7965,10 +7992,10 @@
         <v>119</v>
       </c>
       <c r="V196" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="W196" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X196" t="s">
         <v>238</v>
@@ -7979,10 +8006,10 @@
         <v>119</v>
       </c>
       <c r="V197" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="W197" t="s">
-        <v>226</v>
+        <v>410</v>
       </c>
       <c r="X197" t="s">
         <v>238</v>
@@ -7993,10 +8020,10 @@
         <v>119</v>
       </c>
       <c r="V198" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="W198" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="X198" t="s">
         <v>238</v>
@@ -8007,10 +8034,10 @@
         <v>119</v>
       </c>
       <c r="V199" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="W199" t="s">
-        <v>226</v>
+        <v>410</v>
       </c>
       <c r="X199" t="s">
         <v>238</v>
@@ -8021,10 +8048,10 @@
         <v>119</v>
       </c>
       <c r="V200" t="s">
-        <v>434</v>
+        <v>413</v>
       </c>
       <c r="W200" t="s">
-        <v>226</v>
+        <v>410</v>
       </c>
       <c r="X200" t="s">
         <v>238</v>
@@ -8035,10 +8062,10 @@
         <v>119</v>
       </c>
       <c r="V201" t="s">
-        <v>435</v>
+        <v>414</v>
       </c>
       <c r="W201" t="s">
-        <v>226</v>
+        <v>410</v>
       </c>
       <c r="X201" t="s">
         <v>238</v>
@@ -8049,10 +8076,10 @@
         <v>119</v>
       </c>
       <c r="V202" t="s">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="W202" t="s">
-        <v>226</v>
+        <v>410</v>
       </c>
       <c r="X202" t="s">
         <v>238</v>
@@ -8063,10 +8090,10 @@
         <v>119</v>
       </c>
       <c r="V203" t="s">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="W203" t="s">
-        <v>226</v>
+        <v>410</v>
       </c>
       <c r="X203" t="s">
         <v>238</v>
@@ -8077,10 +8104,10 @@
         <v>119</v>
       </c>
       <c r="V204" t="s">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="W204" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="X204" t="s">
         <v>238</v>
@@ -8091,10 +8118,10 @@
         <v>119</v>
       </c>
       <c r="V205" t="s">
-        <v>439</v>
+        <v>418</v>
       </c>
       <c r="W205" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="X205" t="s">
         <v>238</v>
@@ -8105,10 +8132,10 @@
         <v>119</v>
       </c>
       <c r="V206" t="s">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="W206" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="X206" t="s">
         <v>238</v>
@@ -8119,10 +8146,10 @@
         <v>119</v>
       </c>
       <c r="V207" t="s">
-        <v>441</v>
+        <v>420</v>
       </c>
       <c r="W207" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="X207" t="s">
         <v>238</v>
@@ -8133,10 +8160,10 @@
         <v>119</v>
       </c>
       <c r="V208" t="s">
-        <v>442</v>
+        <v>421</v>
       </c>
       <c r="W208" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X208" t="s">
         <v>238</v>
@@ -8147,10 +8174,10 @@
         <v>119</v>
       </c>
       <c r="V209" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="W209" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X209" t="s">
         <v>238</v>
@@ -8161,10 +8188,10 @@
         <v>119</v>
       </c>
       <c r="V210" t="s">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="W210" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X210" t="s">
         <v>238</v>
@@ -8175,10 +8202,10 @@
         <v>119</v>
       </c>
       <c r="V211" t="s">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="W211" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X211" t="s">
         <v>238</v>
@@ -8189,10 +8216,10 @@
         <v>119</v>
       </c>
       <c r="V212" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="W212" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X212" t="s">
         <v>238</v>
@@ -8203,10 +8230,10 @@
         <v>119</v>
       </c>
       <c r="V213" t="s">
-        <v>447</v>
+        <v>426</v>
       </c>
       <c r="W213" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X213" t="s">
         <v>238</v>
@@ -8217,10 +8244,10 @@
         <v>119</v>
       </c>
       <c r="V214" t="s">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="W214" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X214" t="s">
         <v>238</v>
@@ -8231,10 +8258,10 @@
         <v>119</v>
       </c>
       <c r="V215" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
       <c r="W215" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="X215" t="s">
         <v>238</v>
@@ -8245,10 +8272,10 @@
         <v>119</v>
       </c>
       <c r="V216" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="W216" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X216" t="s">
         <v>238</v>
@@ -8259,10 +8286,10 @@
         <v>119</v>
       </c>
       <c r="V217" t="s">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="W217" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="X217" t="s">
         <v>238</v>
@@ -8273,10 +8300,10 @@
         <v>119</v>
       </c>
       <c r="V218" t="s">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="W218" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="X218" t="s">
         <v>238</v>
@@ -8287,10 +8314,10 @@
         <v>119</v>
       </c>
       <c r="V219" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="W219" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="X219" t="s">
         <v>238</v>
@@ -8301,10 +8328,10 @@
         <v>119</v>
       </c>
       <c r="V220" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="W220" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="X220" t="s">
         <v>238</v>
@@ -8315,10 +8342,10 @@
         <v>119</v>
       </c>
       <c r="V221" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="W221" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="X221" t="s">
         <v>238</v>
@@ -8329,10 +8356,10 @@
         <v>119</v>
       </c>
       <c r="V222" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="W222" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="X222" t="s">
         <v>238</v>
@@ -8343,10 +8370,10 @@
         <v>119</v>
       </c>
       <c r="V223" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="W223" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="X223" t="s">
         <v>238</v>
@@ -8357,10 +8384,10 @@
         <v>119</v>
       </c>
       <c r="V224" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="W224" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="X224" t="s">
         <v>238</v>
@@ -8371,10 +8398,10 @@
         <v>119</v>
       </c>
       <c r="V225" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="W225" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X225" t="s">
         <v>238</v>
@@ -8385,10 +8412,10 @@
         <v>119</v>
       </c>
       <c r="V226" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="W226" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X226" t="s">
         <v>238</v>
@@ -8399,10 +8426,10 @@
         <v>119</v>
       </c>
       <c r="V227" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="W227" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X227" t="s">
         <v>238</v>
@@ -8413,10 +8440,10 @@
         <v>119</v>
       </c>
       <c r="V228" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="W228" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X228" t="s">
         <v>238</v>
@@ -8427,10 +8454,10 @@
         <v>119</v>
       </c>
       <c r="V229" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="W229" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X229" t="s">
         <v>238</v>
@@ -8441,10 +8468,10 @@
         <v>119</v>
       </c>
       <c r="V230" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="W230" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X230" t="s">
         <v>238</v>
@@ -8455,10 +8482,10 @@
         <v>119</v>
       </c>
       <c r="V231" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="W231" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X231" t="s">
         <v>238</v>
@@ -8469,10 +8496,10 @@
         <v>119</v>
       </c>
       <c r="V232" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="W232" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X232" t="s">
         <v>238</v>
@@ -8483,10 +8510,10 @@
         <v>119</v>
       </c>
       <c r="V233" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="W233" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X233" t="s">
         <v>238</v>
@@ -8497,10 +8524,10 @@
         <v>119</v>
       </c>
       <c r="V234" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="W234" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X234" t="s">
         <v>238</v>
@@ -8511,10 +8538,10 @@
         <v>119</v>
       </c>
       <c r="V235" t="s">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="W235" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="X235" t="s">
         <v>238</v>
@@ -8525,10 +8552,10 @@
         <v>119</v>
       </c>
       <c r="V236" t="s">
-        <v>470</v>
+        <v>445</v>
       </c>
       <c r="W236" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X236" t="s">
         <v>238</v>
@@ -8539,10 +8566,10 @@
         <v>119</v>
       </c>
       <c r="V237" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="W237" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="X237" t="s">
         <v>238</v>
@@ -8553,10 +8580,10 @@
         <v>119</v>
       </c>
       <c r="V238" t="s">
-        <v>472</v>
+        <v>446</v>
       </c>
       <c r="W238" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X238" t="s">
         <v>238</v>
@@ -8567,10 +8594,10 @@
         <v>119</v>
       </c>
       <c r="V239" t="s">
-        <v>473</v>
+        <v>446</v>
       </c>
       <c r="W239" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="X239" t="s">
         <v>238</v>
@@ -8581,10 +8608,10 @@
         <v>119</v>
       </c>
       <c r="V240" t="s">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="W240" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="X240" t="s">
         <v>238</v>
@@ -8595,10 +8622,10 @@
         <v>119</v>
       </c>
       <c r="V241" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="W241" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="X241" t="s">
         <v>238</v>
@@ -8609,10 +8636,10 @@
         <v>119</v>
       </c>
       <c r="V242" t="s">
-        <v>476</v>
+        <v>449</v>
       </c>
       <c r="W242" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="X242" t="s">
         <v>238</v>
@@ -8623,10 +8650,10 @@
         <v>119</v>
       </c>
       <c r="V243" t="s">
-        <v>477</v>
+        <v>450</v>
       </c>
       <c r="W243" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="X243" t="s">
         <v>238</v>
@@ -8637,10 +8664,10 @@
         <v>119</v>
       </c>
       <c r="V244" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="W244" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X244" t="s">
         <v>238</v>
@@ -8651,10 +8678,10 @@
         <v>119</v>
       </c>
       <c r="V245" t="s">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="W245" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X245" t="s">
         <v>238</v>
@@ -8665,10 +8692,10 @@
         <v>119</v>
       </c>
       <c r="V246" t="s">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="W246" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X246" t="s">
         <v>238</v>
@@ -8679,10 +8706,10 @@
         <v>119</v>
       </c>
       <c r="V247" t="s">
-        <v>481</v>
+        <v>454</v>
       </c>
       <c r="W247" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X247" t="s">
         <v>238</v>
@@ -8693,10 +8720,10 @@
         <v>119</v>
       </c>
       <c r="V248" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="W248" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X248" t="s">
         <v>238</v>
@@ -8707,10 +8734,10 @@
         <v>119</v>
       </c>
       <c r="V249" t="s">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="W249" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X249" t="s">
         <v>238</v>
@@ -8721,10 +8748,10 @@
         <v>119</v>
       </c>
       <c r="V250" t="s">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="W250" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X250" t="s">
         <v>238</v>
@@ -8735,10 +8762,10 @@
         <v>119</v>
       </c>
       <c r="V251" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="W251" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X251" t="s">
         <v>238</v>
@@ -8749,10 +8776,10 @@
         <v>119</v>
       </c>
       <c r="V252" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="W252" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X252" t="s">
         <v>238</v>
@@ -8763,10 +8790,10 @@
         <v>119</v>
       </c>
       <c r="V253" t="s">
-        <v>487</v>
+        <v>460</v>
       </c>
       <c r="W253" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X253" t="s">
         <v>238</v>
@@ -8777,10 +8804,10 @@
         <v>119</v>
       </c>
       <c r="V254" t="s">
-        <v>488</v>
+        <v>461</v>
       </c>
       <c r="W254" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X254" t="s">
         <v>238</v>
@@ -8791,10 +8818,10 @@
         <v>119</v>
       </c>
       <c r="V255" t="s">
-        <v>489</v>
+        <v>461</v>
       </c>
       <c r="W255" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="X255" t="s">
         <v>238</v>
@@ -8805,10 +8832,10 @@
         <v>119</v>
       </c>
       <c r="V256" t="s">
-        <v>490</v>
+        <v>462</v>
       </c>
       <c r="W256" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X256" t="s">
         <v>238</v>
@@ -8819,10 +8846,10 @@
         <v>119</v>
       </c>
       <c r="V257" t="s">
-        <v>491</v>
+        <v>462</v>
       </c>
       <c r="W257" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="X257" t="s">
         <v>238</v>
@@ -8833,10 +8860,10 @@
         <v>119</v>
       </c>
       <c r="V258" t="s">
-        <v>492</v>
+        <v>463</v>
       </c>
       <c r="W258" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="X258" t="s">
         <v>238</v>
@@ -8847,10 +8874,10 @@
         <v>119</v>
       </c>
       <c r="V259" t="s">
-        <v>493</v>
+        <v>463</v>
       </c>
       <c r="W259" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="X259" t="s">
         <v>238</v>
@@ -8861,13 +8888,13 @@
         <v>119</v>
       </c>
       <c r="V260" t="s">
-        <v>493</v>
+        <v>464</v>
       </c>
       <c r="W260" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="X260" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="261" spans="21:24" x14ac:dyDescent="0.45">
@@ -8875,10 +8902,10 @@
         <v>119</v>
       </c>
       <c r="V261" t="s">
-        <v>494</v>
+        <v>465</v>
       </c>
       <c r="W261" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="X261" t="s">
         <v>238</v>
@@ -8889,13 +8916,13 @@
         <v>119</v>
       </c>
       <c r="V262" t="s">
-        <v>494</v>
+        <v>466</v>
       </c>
       <c r="W262" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="X262" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="263" spans="21:24" x14ac:dyDescent="0.45">
@@ -8903,10 +8930,10 @@
         <v>119</v>
       </c>
       <c r="V263" t="s">
-        <v>495</v>
+        <v>467</v>
       </c>
       <c r="W263" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="X263" t="s">
         <v>238</v>
@@ -8917,13 +8944,13 @@
         <v>119</v>
       </c>
       <c r="V264" t="s">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="W264" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="X264" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="265" spans="21:24" x14ac:dyDescent="0.45">
@@ -8931,10 +8958,10 @@
         <v>119</v>
       </c>
       <c r="V265" t="s">
-        <v>496</v>
+        <v>469</v>
       </c>
       <c r="W265" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="X265" t="s">
         <v>238</v>
@@ -8945,13 +8972,13 @@
         <v>119</v>
       </c>
       <c r="V266" t="s">
-        <v>496</v>
+        <v>470</v>
       </c>
       <c r="W266" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="X266" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="267" spans="21:24" x14ac:dyDescent="0.45">
@@ -8959,10 +8986,10 @@
         <v>119</v>
       </c>
       <c r="V267" t="s">
-        <v>497</v>
+        <v>471</v>
       </c>
       <c r="W267" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="X267" t="s">
         <v>238</v>
@@ -8973,13 +9000,13 @@
         <v>119</v>
       </c>
       <c r="V268" t="s">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c r="W268" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="X268" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="269" spans="21:24" x14ac:dyDescent="0.45">
@@ -8987,10 +9014,10 @@
         <v>119</v>
       </c>
       <c r="V269" t="s">
-        <v>498</v>
+        <v>473</v>
       </c>
       <c r="W269" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="X269" t="s">
         <v>238</v>
@@ -9001,13 +9028,13 @@
         <v>119</v>
       </c>
       <c r="V270" t="s">
-        <v>498</v>
+        <v>474</v>
       </c>
       <c r="W270" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="X270" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="271" spans="21:24" x14ac:dyDescent="0.45">
@@ -9015,10 +9042,10 @@
         <v>119</v>
       </c>
       <c r="V271" t="s">
-        <v>499</v>
+        <v>475</v>
       </c>
       <c r="W271" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="X271" t="s">
         <v>238</v>
@@ -9029,13 +9056,13 @@
         <v>119</v>
       </c>
       <c r="V272" t="s">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="W272" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="X272" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="273" spans="21:24" x14ac:dyDescent="0.45">
@@ -9043,10 +9070,10 @@
         <v>119</v>
       </c>
       <c r="V273" t="s">
-        <v>500</v>
+        <v>477</v>
       </c>
       <c r="W273" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="X273" t="s">
         <v>238</v>
@@ -9057,13 +9084,13 @@
         <v>119</v>
       </c>
       <c r="V274" t="s">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="W274" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="X274" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="275" spans="21:24" x14ac:dyDescent="0.45">
@@ -9071,10 +9098,10 @@
         <v>119</v>
       </c>
       <c r="V275" t="s">
-        <v>501</v>
+        <v>478</v>
       </c>
       <c r="W275" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="X275" t="s">
         <v>238</v>
@@ -9085,13 +9112,13 @@
         <v>119</v>
       </c>
       <c r="V276" t="s">
-        <v>501</v>
+        <v>479</v>
       </c>
       <c r="W276" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="X276" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="277" spans="21:24" x14ac:dyDescent="0.45">
@@ -9099,10 +9126,10 @@
         <v>119</v>
       </c>
       <c r="V277" t="s">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="W277" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="X277" t="s">
         <v>238</v>
@@ -9113,13 +9140,13 @@
         <v>119</v>
       </c>
       <c r="V278" t="s">
-        <v>502</v>
+        <v>480</v>
       </c>
       <c r="W278" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="X278" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="279" spans="21:24" x14ac:dyDescent="0.45">
@@ -9127,10 +9154,10 @@
         <v>119</v>
       </c>
       <c r="V279" t="s">
-        <v>503</v>
+        <v>480</v>
       </c>
       <c r="W279" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="X279" t="s">
         <v>238</v>
@@ -9141,13 +9168,13 @@
         <v>119</v>
       </c>
       <c r="V280" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="W280" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="X280" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="281" spans="21:24" x14ac:dyDescent="0.45">
@@ -9155,10 +9182,10 @@
         <v>119</v>
       </c>
       <c r="V281" t="s">
-        <v>504</v>
+        <v>482</v>
       </c>
       <c r="W281" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="X281" t="s">
         <v>238</v>
@@ -9169,13 +9196,13 @@
         <v>119</v>
       </c>
       <c r="V282" t="s">
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="W282" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="X282" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="283" spans="21:24" x14ac:dyDescent="0.45">
@@ -9183,10 +9210,10 @@
         <v>119</v>
       </c>
       <c r="V283" t="s">
-        <v>505</v>
+        <v>484</v>
       </c>
       <c r="W283" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="X283" t="s">
         <v>238</v>
@@ -9197,13 +9224,13 @@
         <v>119</v>
       </c>
       <c r="V284" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
       <c r="W284" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="X284" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="285" spans="21:24" x14ac:dyDescent="0.45">
@@ -9211,10 +9238,10 @@
         <v>119</v>
       </c>
       <c r="V285" t="s">
-        <v>506</v>
+        <v>486</v>
       </c>
       <c r="W285" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="X285" t="s">
         <v>238</v>
@@ -9225,13 +9252,13 @@
         <v>119</v>
       </c>
       <c r="V286" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="W286" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="X286" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="287" spans="21:24" x14ac:dyDescent="0.45">
@@ -9239,10 +9266,10 @@
         <v>119</v>
       </c>
       <c r="V287" t="s">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="W287" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="X287" t="s">
         <v>238</v>
@@ -9253,13 +9280,13 @@
         <v>119</v>
       </c>
       <c r="V288" t="s">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="W288" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="X288" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="289" spans="21:24" x14ac:dyDescent="0.45">
@@ -9267,10 +9294,10 @@
         <v>119</v>
       </c>
       <c r="V289" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="W289" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="X289" t="s">
         <v>238</v>
@@ -9281,13 +9308,13 @@
         <v>119</v>
       </c>
       <c r="V290" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="W290" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="X290" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="291" spans="21:24" x14ac:dyDescent="0.45">
@@ -9295,10 +9322,10 @@
         <v>119</v>
       </c>
       <c r="V291" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="W291" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="X291" t="s">
         <v>238</v>
@@ -9309,13 +9336,13 @@
         <v>119</v>
       </c>
       <c r="V292" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="W292" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="X292" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="293" spans="21:24" x14ac:dyDescent="0.45">
@@ -9323,10 +9350,10 @@
         <v>119</v>
       </c>
       <c r="V293" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="W293" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="X293" t="s">
         <v>238</v>
@@ -9337,13 +9364,13 @@
         <v>119</v>
       </c>
       <c r="V294" t="s">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="W294" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="X294" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="295" spans="21:24" x14ac:dyDescent="0.45">
@@ -9351,10 +9378,10 @@
         <v>119</v>
       </c>
       <c r="V295" t="s">
-        <v>511</v>
+        <v>495</v>
       </c>
       <c r="W295" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="X295" t="s">
         <v>238</v>
@@ -9365,13 +9392,13 @@
         <v>119</v>
       </c>
       <c r="V296" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="W296" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="X296" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="297" spans="21:24" x14ac:dyDescent="0.45">
@@ -9379,10 +9406,10 @@
         <v>119</v>
       </c>
       <c r="V297" t="s">
-        <v>512</v>
+        <v>496</v>
       </c>
       <c r="W297" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="X297" t="s">
         <v>238</v>
@@ -9393,13 +9420,13 @@
         <v>119</v>
       </c>
       <c r="V298" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="W298" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="X298" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="299" spans="21:24" x14ac:dyDescent="0.45">
@@ -9407,10 +9434,10 @@
         <v>119</v>
       </c>
       <c r="V299" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="W299" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="X299" t="s">
         <v>238</v>
@@ -9421,13 +9448,13 @@
         <v>119</v>
       </c>
       <c r="V300" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="W300" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="X300" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="301" spans="21:24" x14ac:dyDescent="0.45">
@@ -9435,10 +9462,10 @@
         <v>119</v>
       </c>
       <c r="V301" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="W301" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="X301" t="s">
         <v>238</v>
@@ -9449,13 +9476,13 @@
         <v>119</v>
       </c>
       <c r="V302" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="W302" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="X302" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="303" spans="21:24" x14ac:dyDescent="0.45">
@@ -9463,10 +9490,10 @@
         <v>119</v>
       </c>
       <c r="V303" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="W303" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="X303" t="s">
         <v>238</v>
@@ -9477,13 +9504,13 @@
         <v>119</v>
       </c>
       <c r="V304" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="W304" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="X304" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="305" spans="21:24" x14ac:dyDescent="0.45">
@@ -9491,13 +9518,13 @@
         <v>119</v>
       </c>
       <c r="V305" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="W305" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="X305" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
     </row>
     <row r="306" spans="21:24" x14ac:dyDescent="0.45">
@@ -9505,13 +9532,13 @@
         <v>119</v>
       </c>
       <c r="V306" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="W306" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="X306" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="307" spans="21:24" x14ac:dyDescent="0.45">
@@ -9519,13 +9546,13 @@
         <v>119</v>
       </c>
       <c r="V307" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="W307" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="X307" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
     </row>
     <row r="308" spans="21:24" x14ac:dyDescent="0.45">
@@ -9533,13 +9560,13 @@
         <v>119</v>
       </c>
       <c r="V308" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="W308" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="X308" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="309" spans="21:24" x14ac:dyDescent="0.45">
@@ -9547,13 +9574,13 @@
         <v>119</v>
       </c>
       <c r="V309" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="W309" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="X309" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
     </row>
     <row r="310" spans="21:24" x14ac:dyDescent="0.45">
@@ -9561,13 +9588,13 @@
         <v>119</v>
       </c>
       <c r="V310" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="W310" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="X310" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="311" spans="21:24" x14ac:dyDescent="0.45">
@@ -9575,13 +9602,13 @@
         <v>119</v>
       </c>
       <c r="V311" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="W311" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="X311" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
     </row>
     <row r="312" spans="21:24" x14ac:dyDescent="0.45">
@@ -9589,13 +9616,13 @@
         <v>119</v>
       </c>
       <c r="V312" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="W312" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="X312" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="313" spans="21:24" x14ac:dyDescent="0.45">
@@ -9603,13 +9630,13 @@
         <v>119</v>
       </c>
       <c r="V313" t="s">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="W313" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="X313" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
     </row>
     <row r="314" spans="21:24" x14ac:dyDescent="0.45">
@@ -9617,13 +9644,13 @@
         <v>119</v>
       </c>
       <c r="V314" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="W314" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="X314" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="315" spans="21:24" x14ac:dyDescent="0.45">
@@ -9631,13 +9658,13 @@
         <v>119</v>
       </c>
       <c r="V315" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="W315" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="X315" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
     </row>
     <row r="316" spans="21:24" x14ac:dyDescent="0.45">
@@ -9645,13 +9672,13 @@
         <v>119</v>
       </c>
       <c r="V316" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="W316" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="X316" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
     </row>
     <row r="317" spans="21:24" x14ac:dyDescent="0.45">
@@ -9659,13 +9686,13 @@
         <v>119</v>
       </c>
       <c r="V317" t="s">
-        <v>522</v>
+        <v>508</v>
       </c>
       <c r="W317" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="X317" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
     </row>
     <row r="318" spans="21:24" x14ac:dyDescent="0.45">
@@ -9673,12 +9700,642 @@
         <v>119</v>
       </c>
       <c r="V318" t="s">
+        <v>509</v>
+      </c>
+      <c r="W318" t="s">
+        <v>218</v>
+      </c>
+      <c r="X318" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="319" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U319" t="s">
+        <v>119</v>
+      </c>
+      <c r="V319" t="s">
+        <v>509</v>
+      </c>
+      <c r="W319" t="s">
+        <v>218</v>
+      </c>
+      <c r="X319" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="320" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U320" t="s">
+        <v>119</v>
+      </c>
+      <c r="V320" t="s">
+        <v>510</v>
+      </c>
+      <c r="W320" t="s">
+        <v>219</v>
+      </c>
+      <c r="X320" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="321" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U321" t="s">
+        <v>119</v>
+      </c>
+      <c r="V321" t="s">
+        <v>510</v>
+      </c>
+      <c r="W321" t="s">
+        <v>219</v>
+      </c>
+      <c r="X321" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="322" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U322" t="s">
+        <v>119</v>
+      </c>
+      <c r="V322" t="s">
+        <v>511</v>
+      </c>
+      <c r="W322" t="s">
+        <v>219</v>
+      </c>
+      <c r="X322" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="323" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U323" t="s">
+        <v>119</v>
+      </c>
+      <c r="V323" t="s">
+        <v>511</v>
+      </c>
+      <c r="W323" t="s">
+        <v>219</v>
+      </c>
+      <c r="X323" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="324" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U324" t="s">
+        <v>119</v>
+      </c>
+      <c r="V324" t="s">
+        <v>512</v>
+      </c>
+      <c r="W324" t="s">
+        <v>220</v>
+      </c>
+      <c r="X324" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="325" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U325" t="s">
+        <v>119</v>
+      </c>
+      <c r="V325" t="s">
+        <v>512</v>
+      </c>
+      <c r="W325" t="s">
+        <v>220</v>
+      </c>
+      <c r="X325" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="326" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U326" t="s">
+        <v>119</v>
+      </c>
+      <c r="V326" t="s">
+        <v>513</v>
+      </c>
+      <c r="W326" t="s">
+        <v>220</v>
+      </c>
+      <c r="X326" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="327" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U327" t="s">
+        <v>119</v>
+      </c>
+      <c r="V327" t="s">
+        <v>513</v>
+      </c>
+      <c r="W327" t="s">
+        <v>220</v>
+      </c>
+      <c r="X327" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="328" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U328" t="s">
+        <v>119</v>
+      </c>
+      <c r="V328" t="s">
+        <v>514</v>
+      </c>
+      <c r="W328" t="s">
+        <v>221</v>
+      </c>
+      <c r="X328" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="329" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U329" t="s">
+        <v>119</v>
+      </c>
+      <c r="V329" t="s">
+        <v>514</v>
+      </c>
+      <c r="W329" t="s">
+        <v>221</v>
+      </c>
+      <c r="X329" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="330" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U330" t="s">
+        <v>119</v>
+      </c>
+      <c r="V330" t="s">
+        <v>515</v>
+      </c>
+      <c r="W330" t="s">
+        <v>221</v>
+      </c>
+      <c r="X330" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="331" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U331" t="s">
+        <v>119</v>
+      </c>
+      <c r="V331" t="s">
+        <v>515</v>
+      </c>
+      <c r="W331" t="s">
+        <v>221</v>
+      </c>
+      <c r="X331" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="332" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U332" t="s">
+        <v>119</v>
+      </c>
+      <c r="V332" t="s">
+        <v>516</v>
+      </c>
+      <c r="W332" t="s">
+        <v>222</v>
+      </c>
+      <c r="X332" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="333" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U333" t="s">
+        <v>119</v>
+      </c>
+      <c r="V333" t="s">
+        <v>516</v>
+      </c>
+      <c r="W333" t="s">
+        <v>222</v>
+      </c>
+      <c r="X333" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="334" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U334" t="s">
+        <v>119</v>
+      </c>
+      <c r="V334" t="s">
+        <v>517</v>
+      </c>
+      <c r="W334" t="s">
+        <v>222</v>
+      </c>
+      <c r="X334" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="335" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U335" t="s">
+        <v>119</v>
+      </c>
+      <c r="V335" t="s">
+        <v>517</v>
+      </c>
+      <c r="W335" t="s">
+        <v>222</v>
+      </c>
+      <c r="X335" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="336" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U336" t="s">
+        <v>119</v>
+      </c>
+      <c r="V336" t="s">
+        <v>518</v>
+      </c>
+      <c r="W336" t="s">
+        <v>223</v>
+      </c>
+      <c r="X336" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="337" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U337" t="s">
+        <v>119</v>
+      </c>
+      <c r="V337" t="s">
+        <v>518</v>
+      </c>
+      <c r="W337" t="s">
+        <v>223</v>
+      </c>
+      <c r="X337" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="338" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U338" t="s">
+        <v>119</v>
+      </c>
+      <c r="V338" t="s">
+        <v>519</v>
+      </c>
+      <c r="W338" t="s">
+        <v>223</v>
+      </c>
+      <c r="X338" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="339" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U339" t="s">
+        <v>119</v>
+      </c>
+      <c r="V339" t="s">
+        <v>519</v>
+      </c>
+      <c r="W339" t="s">
+        <v>223</v>
+      </c>
+      <c r="X339" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="340" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U340" t="s">
+        <v>119</v>
+      </c>
+      <c r="V340" t="s">
+        <v>520</v>
+      </c>
+      <c r="W340" t="s">
+        <v>224</v>
+      </c>
+      <c r="X340" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="341" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U341" t="s">
+        <v>119</v>
+      </c>
+      <c r="V341" t="s">
+        <v>520</v>
+      </c>
+      <c r="W341" t="s">
+        <v>224</v>
+      </c>
+      <c r="X341" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="342" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U342" t="s">
+        <v>119</v>
+      </c>
+      <c r="V342" t="s">
+        <v>521</v>
+      </c>
+      <c r="W342" t="s">
+        <v>224</v>
+      </c>
+      <c r="X342" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="343" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U343" t="s">
+        <v>119</v>
+      </c>
+      <c r="V343" t="s">
+        <v>521</v>
+      </c>
+      <c r="W343" t="s">
+        <v>224</v>
+      </c>
+      <c r="X343" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="344" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U344" t="s">
+        <v>119</v>
+      </c>
+      <c r="V344" t="s">
         <v>522</v>
       </c>
-      <c r="W318" t="s">
+      <c r="W344" t="s">
+        <v>225</v>
+      </c>
+      <c r="X344" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="345" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U345" t="s">
+        <v>119</v>
+      </c>
+      <c r="V345" t="s">
+        <v>522</v>
+      </c>
+      <c r="W345" t="s">
+        <v>225</v>
+      </c>
+      <c r="X345" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="346" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U346" t="s">
+        <v>119</v>
+      </c>
+      <c r="V346" t="s">
+        <v>523</v>
+      </c>
+      <c r="W346" t="s">
+        <v>225</v>
+      </c>
+      <c r="X346" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="347" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U347" t="s">
+        <v>119</v>
+      </c>
+      <c r="V347" t="s">
+        <v>523</v>
+      </c>
+      <c r="W347" t="s">
+        <v>225</v>
+      </c>
+      <c r="X347" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="348" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U348" t="s">
+        <v>119</v>
+      </c>
+      <c r="V348" t="s">
+        <v>524</v>
+      </c>
+      <c r="W348" t="s">
+        <v>226</v>
+      </c>
+      <c r="X348" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="349" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U349" t="s">
+        <v>119</v>
+      </c>
+      <c r="V349" t="s">
+        <v>524</v>
+      </c>
+      <c r="W349" t="s">
+        <v>226</v>
+      </c>
+      <c r="X349" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="350" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U350" t="s">
+        <v>119</v>
+      </c>
+      <c r="V350" t="s">
+        <v>525</v>
+      </c>
+      <c r="W350" t="s">
+        <v>226</v>
+      </c>
+      <c r="X350" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="351" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U351" t="s">
+        <v>119</v>
+      </c>
+      <c r="V351" t="s">
+        <v>525</v>
+      </c>
+      <c r="W351" t="s">
+        <v>226</v>
+      </c>
+      <c r="X351" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="352" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U352" t="s">
+        <v>119</v>
+      </c>
+      <c r="V352" t="s">
+        <v>526</v>
+      </c>
+      <c r="W352" t="s">
+        <v>227</v>
+      </c>
+      <c r="X352" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="353" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U353" t="s">
+        <v>119</v>
+      </c>
+      <c r="V353" t="s">
+        <v>526</v>
+      </c>
+      <c r="W353" t="s">
+        <v>227</v>
+      </c>
+      <c r="X353" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="354" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U354" t="s">
+        <v>119</v>
+      </c>
+      <c r="V354" t="s">
+        <v>527</v>
+      </c>
+      <c r="W354" t="s">
+        <v>227</v>
+      </c>
+      <c r="X354" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="355" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U355" t="s">
+        <v>119</v>
+      </c>
+      <c r="V355" t="s">
+        <v>527</v>
+      </c>
+      <c r="W355" t="s">
+        <v>227</v>
+      </c>
+      <c r="X355" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="356" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U356" t="s">
+        <v>119</v>
+      </c>
+      <c r="V356" t="s">
+        <v>528</v>
+      </c>
+      <c r="W356" t="s">
+        <v>228</v>
+      </c>
+      <c r="X356" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="357" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U357" t="s">
+        <v>119</v>
+      </c>
+      <c r="V357" t="s">
+        <v>528</v>
+      </c>
+      <c r="W357" t="s">
+        <v>228</v>
+      </c>
+      <c r="X357" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="358" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U358" t="s">
+        <v>119</v>
+      </c>
+      <c r="V358" t="s">
+        <v>529</v>
+      </c>
+      <c r="W358" t="s">
+        <v>228</v>
+      </c>
+      <c r="X358" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="359" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U359" t="s">
+        <v>119</v>
+      </c>
+      <c r="V359" t="s">
+        <v>529</v>
+      </c>
+      <c r="W359" t="s">
+        <v>228</v>
+      </c>
+      <c r="X359" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="360" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U360" t="s">
+        <v>119</v>
+      </c>
+      <c r="V360" t="s">
+        <v>530</v>
+      </c>
+      <c r="W360" t="s">
         <v>229</v>
       </c>
-      <c r="X318" t="s">
+      <c r="X360" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="361" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U361" t="s">
+        <v>119</v>
+      </c>
+      <c r="V361" t="s">
+        <v>530</v>
+      </c>
+      <c r="W361" t="s">
+        <v>229</v>
+      </c>
+      <c r="X361" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="362" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U362" t="s">
+        <v>119</v>
+      </c>
+      <c r="V362" t="s">
+        <v>531</v>
+      </c>
+      <c r="W362" t="s">
+        <v>229</v>
+      </c>
+      <c r="X362" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="363" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U363" t="s">
+        <v>119</v>
+      </c>
+      <c r="V363" t="s">
+        <v>531</v>
+      </c>
+      <c r="W363" t="s">
+        <v>229</v>
+      </c>
+      <c r="X363" t="s">
         <v>215</v>
       </c>
     </row>
@@ -9688,7 +10345,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3658E24B-FBA1-4F15-8854-135CC6C6D524}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81624397-2C0E-4003-B2E7-F1E0C7867BB2}">
   <dimension ref="B9:L39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -21612,13 +22269,13 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2135B8A7-B9FA-4951-A8F1-FAE003F1D437}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05D540AB-FEC5-46CC-826F-105A98B05319}">
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C1" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
@@ -21626,12 +22283,12 @@
         <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="B4" t="s">
         <v>69</v>
@@ -21640,10 +22297,10 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="E4" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="G4" t="s">
         <v>69</v>
@@ -21652,18 +22309,18 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B5" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="C5" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -21672,10 +22329,10 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="H5" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -21683,13 +22340,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B6" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="C6" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -21698,10 +22355,10 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="H6" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -21709,13 +22366,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B7" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C7" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -21724,10 +22381,10 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="H7" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -21735,13 +22392,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B8" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="C8" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -21750,10 +22407,10 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="H8" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -21761,13 +22418,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B9" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="C9" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -21776,10 +22433,10 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="H9" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -21787,13 +22444,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B10" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="C10" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -21802,10 +22459,10 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="H10" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -21813,13 +22470,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B11" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="C11" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -21828,10 +22485,10 @@
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="H11" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -21839,13 +22496,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B12" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="C12" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -21854,10 +22511,10 @@
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="H12" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -21865,13 +22522,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B13" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="C13" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -21880,10 +22537,10 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="H13" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -21891,13 +22548,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B14" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="C14" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -21906,10 +22563,10 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="H14" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -21917,13 +22574,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B15" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="C15" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -21932,10 +22589,10 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="H15" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -21943,13 +22600,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B16" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="C16" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -21958,10 +22615,10 @@
         <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="H16" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -21969,13 +22626,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B17" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="C17" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -21984,10 +22641,10 @@
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="H17" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -21995,13 +22652,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B18" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="C18" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -22010,10 +22667,10 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="H18" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -22021,13 +22678,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B19" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="C19" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -22036,10 +22693,10 @@
         <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="H19" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -22047,13 +22704,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B20" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="C20" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -22062,10 +22719,10 @@
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="H20" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -22073,13 +22730,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B21" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="C21" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -22088,10 +22745,10 @@
         <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="H21" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -22099,13 +22756,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B22" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="C22" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -22114,10 +22771,10 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="H22" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -22125,13 +22782,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B23" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="C23" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -22140,10 +22797,10 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="H23" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -22151,13 +22808,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B24" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="C24" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -22166,10 +22823,10 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="H24" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -22177,13 +22834,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B25" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="C25" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -22192,10 +22849,10 @@
         <v>2</v>
       </c>
       <c r="G25" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="H25" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -22203,13 +22860,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B26" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="C26" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -22218,10 +22875,10 @@
         <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="H26" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -22229,13 +22886,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B27" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="C27" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -22244,10 +22901,10 @@
         <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="H27" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -22255,13 +22912,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B28" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="C28" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -22270,10 +22927,10 @@
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="H28" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -22281,13 +22938,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B29" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="C29" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -22296,10 +22953,10 @@
         <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="H29" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -22307,13 +22964,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B30" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="C30" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -22322,10 +22979,10 @@
         <v>2</v>
       </c>
       <c r="G30" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="H30" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -22333,13 +22990,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B31" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="C31" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -22348,10 +23005,10 @@
         <v>2</v>
       </c>
       <c r="G31" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="H31" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -22359,13 +23016,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="B32" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="C32" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -22374,10 +23031,10 @@
         <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="H32" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="I32">
         <v>-1</v>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECEA87B0-D138-4E33-BD56-9F6D76E38D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB0FA574-F5C7-48F9-A39E-A46908BBEBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2432,7 +2432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F258A61-617F-40B5-90A4-0CC5474F8BD2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C024E513-7AC9-4AF4-A0C5-671F82E4C01E}">
   <dimension ref="B2:AG363"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10345,7 +10345,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81624397-2C0E-4003-B2E7-F1E0C7867BB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C735372A-6D38-4B41-8C5A-C89A1E7EF69F}">
   <dimension ref="B9:L39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22269,7 +22269,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05D540AB-FEC5-46CC-826F-105A98B05319}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC421D09-0DA5-4299-960F-EEEE9CA7405F}">
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CB0FA574-F5C7-48F9-A39E-A46908BBEBCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EF596BD-D47C-4BC0-B35C-D4628AAC0756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2432,7 +2432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C024E513-7AC9-4AF4-A0C5-671F82E4C01E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DEFE939-5E36-4888-8B72-1456087C6C55}">
   <dimension ref="B2:AG363"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10345,7 +10345,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C735372A-6D38-4B41-8C5A-C89A1E7EF69F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F92438-17C3-4EE7-9F7A-A83EB168661B}">
   <dimension ref="B9:L39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22269,7 +22269,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC421D09-0DA5-4299-960F-EEEE9CA7405F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045E9BB9-05A0-443A-BCD3-DC3D047C21CA}">
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EF596BD-D47C-4BC0-B35C-D4628AAC0756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F471035F-E865-4511-AE2B-BCCDAD8D5A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="grids" sheetId="6" r:id="rId1"/>
@@ -18,7 +18,8 @@
     <sheet name="Veda" sheetId="1" r:id="rId3"/>
     <sheet name="buildrates" sheetId="4" r:id="rId4"/>
     <sheet name="historical_data_long" sheetId="3" r:id="rId5"/>
-    <sheet name="vre agg cap" sheetId="7" r:id="rId6"/>
+    <sheet name="co2_network" sheetId="7" r:id="rId6"/>
+    <sheet name="vre agg cap" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -126,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4159" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4435" uniqueCount="700">
   <si>
     <t>~TFM_INS-AT</t>
   </si>
@@ -1760,6 +1761,228 @@
     <t>all</t>
   </si>
   <si>
+    <t>act_cum</t>
+  </si>
+  <si>
+    <t>sto_ogci10893_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci10894_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci10895_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci10896_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci10897_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci10898_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci10899_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci10900_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci10901_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci10902_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci10903_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci10904_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci10906_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci10907_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci11249_HRV</t>
+  </si>
+  <si>
+    <t>sto_ogci11250_HRV</t>
+  </si>
+  <si>
+    <t>act_cost</t>
+  </si>
+  <si>
+    <t>p_co2_Vinkovci_HRV-ogci10897</t>
+  </si>
+  <si>
+    <t>p_co2_Sibenik_HRV-ogci10907</t>
+  </si>
+  <si>
+    <t>p_co2_Knin_HRV-ogci10907</t>
+  </si>
+  <si>
+    <t>p_co2_Sisak_HRV-ogci10893</t>
+  </si>
+  <si>
+    <t>p_co2_Pula_HRV-ogci10904</t>
+  </si>
+  <si>
+    <t>p_co2_Ogulin_HRV-ogci10899</t>
+  </si>
+  <si>
+    <t>p_co2_Split_HRV-ogci10907</t>
+  </si>
+  <si>
+    <t>p_co2_KastelStari_HRV-ogci10907</t>
+  </si>
+  <si>
+    <t>p_co2_Viskovo_HRV-ogci10904</t>
+  </si>
+  <si>
+    <t>p_co2_Rijeka_HRV-ogci10904</t>
+  </si>
+  <si>
+    <t>p_co2_VelikaGorica_HRV-ogci10899</t>
+  </si>
+  <si>
+    <t>p_co2_Sesvete_HRV-ogci10899</t>
+  </si>
+  <si>
+    <t>p_co2_Zagreb_HRV-ogci10899</t>
+  </si>
+  <si>
+    <t>p_co2_Osijek_HRV-ogci10897</t>
+  </si>
+  <si>
+    <t>p_co2_Kutina_HRV-ogci10895</t>
+  </si>
+  <si>
+    <t>p_co2_Sisak_HRV-ogci10894</t>
+  </si>
+  <si>
+    <t>p_co2_Kutina_HRV-ogci10896</t>
+  </si>
+  <si>
+    <t>p_co2_Sibenik_HRV-ogci10898</t>
+  </si>
+  <si>
+    <t>p_co2_Zagreb_HRV-ogci10900</t>
+  </si>
+  <si>
+    <t>p_co2_Kutina_HRV-ogci10901</t>
+  </si>
+  <si>
+    <t>p_co2_Osijek_HRV-ogci10902</t>
+  </si>
+  <si>
+    <t>p_co2_Pula_HRV-ogci10903</t>
+  </si>
+  <si>
+    <t>p_co2_Sibenik_HRV-ogci10906</t>
+  </si>
+  <si>
+    <t>p_co2_Sibenik_HRV-ogci11249</t>
+  </si>
+  <si>
+    <t>p_co2_Sibenik_HRV-ogci11250</t>
+  </si>
+  <si>
+    <t>flo_emis</t>
+  </si>
+  <si>
+    <t>co2_Vinkovci_HRV</t>
+  </si>
+  <si>
+    <t>co2_Sibenik_HRV</t>
+  </si>
+  <si>
+    <t>co2_Knin_HRV</t>
+  </si>
+  <si>
+    <t>co2_Sisak_HRV</t>
+  </si>
+  <si>
+    <t>co2_Pula_HRV</t>
+  </si>
+  <si>
+    <t>co2_Ogulin_HRV</t>
+  </si>
+  <si>
+    <t>co2_Split_HRV</t>
+  </si>
+  <si>
+    <t>co2_KastelStari_HRV</t>
+  </si>
+  <si>
+    <t>co2_Viskovo_HRV</t>
+  </si>
+  <si>
+    <t>co2_Rijeka_HRV</t>
+  </si>
+  <si>
+    <t>co2_VelikaGorica_HRV</t>
+  </si>
+  <si>
+    <t>co2_Sesvete_HRV</t>
+  </si>
+  <si>
+    <t>co2_Zagreb_HRV</t>
+  </si>
+  <si>
+    <t>co2_Osijek_HRV</t>
+  </si>
+  <si>
+    <t>co2_Kutina_HRV</t>
+  </si>
+  <si>
+    <t>ep_gas_steam_turbine_G100000400055-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400050-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_oil_gas_turbine_G100000410800-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_oil_combined_cycle_G100000400056-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_oil_steam_turbine_G100001031130_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_oil_combined_cycle_G100000400059-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_m_coal_subcritical_G100000108044_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_coal_subcritical_G100000108045_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400052-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_oil_combined_cycle_G100001031132-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_oil_gas_turbine_G100000400053-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400049-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_oil_combined_cycle_G100000400058-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100001031110-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_oil_gas_turbine_G100000400054-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>~UC_Sets: R_S: Allregions</t>
   </si>
   <si>
@@ -1863,6 +2086,72 @@
   </si>
   <si>
     <t>elc_spv_HRV_015</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_wof_HRV_001</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_001</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_wof_HRV_002</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_002</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_wof_HRV_003</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_003</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_wof_HRV_004</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_004</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_wof_HRV_005</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_005</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_wof_HRV_006</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_006</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_wof_HRV_007</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_007</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_wof_HRV_008</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_008</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_wof_HRV_009</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_009</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_wof_HRV_010</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_010</t>
+  </si>
+  <si>
+    <t>UCE_elcagg_wof_HRV_011</t>
+  </si>
+  <si>
+    <t>elc_wof_HRV_011</t>
   </si>
   <si>
     <t>UCE_elcagg_won_HRV_001</t>
@@ -2432,7 +2721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DEFE939-5E36-4888-8B72-1456087C6C55}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D78D1F-5518-46B2-8F4D-B435FE24898B}">
   <dimension ref="B2:AG363"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10345,7 +10634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28F92438-17C3-4EE7-9F7A-A83EB168661B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE83CD4B-EB9F-46B4-9394-C67172FA6ED9}">
   <dimension ref="B9:L39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22269,13 +22558,1038 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{045E9BB9-05A0-443A-BCD3-DC3D047C21CA}">
-  <dimension ref="A1:I32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94D3F4A-4BD8-49CA-8D9F-95DED6F64E25}">
+  <dimension ref="B2:Q48"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>533</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" t="s">
+        <v>560</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>543</v>
+      </c>
+      <c r="C4" t="s">
+        <v>544</v>
+      </c>
+      <c r="D4" t="s">
+        <v>534</v>
+      </c>
+      <c r="E4">
+        <v>310000</v>
+      </c>
+      <c r="H4" t="s">
+        <v>561</v>
+      </c>
+      <c r="I4">
+        <v>2.1988118695251725E-3</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+      <c r="O4" t="s">
+        <v>240</v>
+      </c>
+      <c r="P4" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q4">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>543</v>
+      </c>
+      <c r="C5" t="s">
+        <v>545</v>
+      </c>
+      <c r="D5" t="s">
+        <v>534</v>
+      </c>
+      <c r="E5">
+        <v>269700</v>
+      </c>
+      <c r="H5" t="s">
+        <v>562</v>
+      </c>
+      <c r="I5">
+        <v>3.2335480339334066E-3</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" t="s">
+        <v>251</v>
+      </c>
+      <c r="P5" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q5">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>543</v>
+      </c>
+      <c r="C6" t="s">
+        <v>546</v>
+      </c>
+      <c r="D6" t="s">
+        <v>534</v>
+      </c>
+      <c r="E6">
+        <v>281700</v>
+      </c>
+      <c r="H6" t="s">
+        <v>563</v>
+      </c>
+      <c r="I6">
+        <v>4.9256677198809161E-3</v>
+      </c>
+      <c r="N6" t="s">
+        <v>31</v>
+      </c>
+      <c r="O6" t="s">
+        <v>258</v>
+      </c>
+      <c r="P6" t="s">
+        <v>588</v>
+      </c>
+      <c r="Q6">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>543</v>
+      </c>
+      <c r="C7" t="s">
+        <v>547</v>
+      </c>
+      <c r="D7" t="s">
+        <v>534</v>
+      </c>
+      <c r="E7">
+        <v>3360700</v>
+      </c>
+      <c r="H7" t="s">
+        <v>564</v>
+      </c>
+      <c r="I7">
+        <v>1.6450184286063054E-3</v>
+      </c>
+      <c r="N7" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" t="s">
+        <v>269</v>
+      </c>
+      <c r="P7" t="s">
+        <v>588</v>
+      </c>
+      <c r="Q7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>543</v>
+      </c>
+      <c r="C8" t="s">
+        <v>548</v>
+      </c>
+      <c r="D8" t="s">
+        <v>534</v>
+      </c>
+      <c r="E8">
+        <v>143100</v>
+      </c>
+      <c r="H8" t="s">
+        <v>565</v>
+      </c>
+      <c r="I8">
+        <v>5.6881629526225235E-3</v>
+      </c>
+      <c r="N8" t="s">
+        <v>31</v>
+      </c>
+      <c r="O8" t="s">
+        <v>276</v>
+      </c>
+      <c r="P8" t="s">
+        <v>589</v>
+      </c>
+      <c r="Q8">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>543</v>
+      </c>
+      <c r="C9" t="s">
+        <v>549</v>
+      </c>
+      <c r="D9" t="s">
+        <v>534</v>
+      </c>
+      <c r="E9">
+        <v>327050</v>
+      </c>
+      <c r="H9" t="s">
+        <v>566</v>
+      </c>
+      <c r="I9">
+        <v>7.3386829516396959E-3</v>
+      </c>
+      <c r="N9" t="s">
+        <v>31</v>
+      </c>
+      <c r="O9" t="s">
+        <v>287</v>
+      </c>
+      <c r="P9" t="s">
+        <v>589</v>
+      </c>
+      <c r="Q9">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>543</v>
+      </c>
+      <c r="C10" t="s">
+        <v>550</v>
+      </c>
+      <c r="D10" t="s">
+        <v>534</v>
+      </c>
+      <c r="E10">
+        <v>10100</v>
+      </c>
+      <c r="H10" t="s">
+        <v>567</v>
+      </c>
+      <c r="I10">
+        <v>3.8635650944556376E-3</v>
+      </c>
+      <c r="N10" t="s">
+        <v>31</v>
+      </c>
+      <c r="O10" t="s">
+        <v>294</v>
+      </c>
+      <c r="P10" t="s">
+        <v>590</v>
+      </c>
+      <c r="Q10">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>543</v>
+      </c>
+      <c r="C11" t="s">
+        <v>551</v>
+      </c>
+      <c r="D11" t="s">
+        <v>534</v>
+      </c>
+      <c r="E11">
+        <v>42800</v>
+      </c>
+      <c r="H11" t="s">
+        <v>568</v>
+      </c>
+      <c r="I11">
+        <v>5.5153356454166365E-3</v>
+      </c>
+      <c r="N11" t="s">
+        <v>31</v>
+      </c>
+      <c r="O11" t="s">
+        <v>304</v>
+      </c>
+      <c r="P11" t="s">
+        <v>590</v>
+      </c>
+      <c r="Q11">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>543</v>
+      </c>
+      <c r="C12" t="s">
+        <v>552</v>
+      </c>
+      <c r="D12" t="s">
+        <v>534</v>
+      </c>
+      <c r="E12">
+        <v>31600</v>
+      </c>
+      <c r="H12" t="s">
+        <v>569</v>
+      </c>
+      <c r="I12">
+        <v>7.4416280354798713E-3</v>
+      </c>
+      <c r="N12" t="s">
+        <v>31</v>
+      </c>
+      <c r="O12" t="s">
+        <v>311</v>
+      </c>
+      <c r="P12" t="s">
+        <v>591</v>
+      </c>
+      <c r="Q12">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>543</v>
+      </c>
+      <c r="C13" t="s">
+        <v>553</v>
+      </c>
+      <c r="D13" t="s">
+        <v>534</v>
+      </c>
+      <c r="E13">
+        <v>13700</v>
+      </c>
+      <c r="H13" t="s">
+        <v>570</v>
+      </c>
+      <c r="I13">
+        <v>7.443111228989263E-3</v>
+      </c>
+      <c r="N13" t="s">
+        <v>31</v>
+      </c>
+      <c r="O13" t="s">
+        <v>322</v>
+      </c>
+      <c r="P13" t="s">
+        <v>591</v>
+      </c>
+      <c r="Q13">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>543</v>
+      </c>
+      <c r="C14" t="s">
+        <v>554</v>
+      </c>
+      <c r="D14" t="s">
+        <v>534</v>
+      </c>
+      <c r="E14">
+        <v>10500</v>
+      </c>
+      <c r="H14" t="s">
+        <v>571</v>
+      </c>
+      <c r="I14">
+        <v>2.7859830624820687E-3</v>
+      </c>
+      <c r="N14" t="s">
+        <v>31</v>
+      </c>
+      <c r="O14" t="s">
+        <v>329</v>
+      </c>
+      <c r="P14" t="s">
+        <v>592</v>
+      </c>
+      <c r="Q14">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>543</v>
+      </c>
+      <c r="C15" t="s">
+        <v>555</v>
+      </c>
+      <c r="D15" t="s">
+        <v>534</v>
+      </c>
+      <c r="E15">
+        <v>11900</v>
+      </c>
+      <c r="H15" t="s">
+        <v>572</v>
+      </c>
+      <c r="I15">
+        <v>1.666704191569618E-3</v>
+      </c>
+      <c r="N15" t="s">
+        <v>31</v>
+      </c>
+      <c r="O15" t="s">
+        <v>340</v>
+      </c>
+      <c r="P15" t="s">
+        <v>592</v>
+      </c>
+      <c r="Q15">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>543</v>
+      </c>
+      <c r="C16" t="s">
+        <v>556</v>
+      </c>
+      <c r="D16" t="s">
+        <v>534</v>
+      </c>
+      <c r="E16">
+        <v>13000</v>
+      </c>
+      <c r="H16" t="s">
+        <v>573</v>
+      </c>
+      <c r="I16">
+        <v>2.0116471896766755E-3</v>
+      </c>
+      <c r="N16" t="s">
+        <v>31</v>
+      </c>
+      <c r="O16" t="s">
+        <v>347</v>
+      </c>
+      <c r="P16" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q16">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>543</v>
+      </c>
+      <c r="C17" t="s">
+        <v>557</v>
+      </c>
+      <c r="D17" t="s">
+        <v>534</v>
+      </c>
+      <c r="E17">
+        <v>30000</v>
+      </c>
+      <c r="H17" t="s">
+        <v>574</v>
+      </c>
+      <c r="I17">
+        <v>3.8891401331293395E-4</v>
+      </c>
+      <c r="N17" t="s">
+        <v>31</v>
+      </c>
+      <c r="O17" t="s">
+        <v>358</v>
+      </c>
+      <c r="P17" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q17">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>543</v>
+      </c>
+      <c r="C18" t="s">
+        <v>558</v>
+      </c>
+      <c r="D18" t="s">
+        <v>534</v>
+      </c>
+      <c r="E18">
+        <v>26000</v>
+      </c>
+      <c r="H18" t="s">
+        <v>575</v>
+      </c>
+      <c r="I18">
+        <v>2.7870844019612412E-3</v>
+      </c>
+      <c r="N18" t="s">
+        <v>31</v>
+      </c>
+      <c r="O18" t="s">
+        <v>365</v>
+      </c>
+      <c r="P18" t="s">
+        <v>594</v>
+      </c>
+      <c r="Q18">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>543</v>
+      </c>
+      <c r="C19" t="s">
+        <v>559</v>
+      </c>
+      <c r="D19" t="s">
+        <v>534</v>
+      </c>
+      <c r="E19">
+        <v>15000</v>
+      </c>
+      <c r="H19" t="s">
+        <v>576</v>
+      </c>
+      <c r="I19">
+        <v>1.6452485981959791E-3</v>
+      </c>
+      <c r="N19" t="s">
+        <v>31</v>
+      </c>
+      <c r="O19" t="s">
+        <v>376</v>
+      </c>
+      <c r="P19" t="s">
+        <v>594</v>
+      </c>
+      <c r="Q19">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="H20" t="s">
+        <v>577</v>
+      </c>
+      <c r="I20">
+        <v>4.4918887080809137E-3</v>
+      </c>
+      <c r="N20" t="s">
+        <v>31</v>
+      </c>
+      <c r="O20" t="s">
+        <v>383</v>
+      </c>
+      <c r="P20" t="s">
+        <v>595</v>
+      </c>
+      <c r="Q20">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="H21" t="s">
+        <v>578</v>
+      </c>
+      <c r="I21">
+        <v>3.9209872316450121E-3</v>
+      </c>
+      <c r="N21" t="s">
+        <v>31</v>
+      </c>
+      <c r="O21" t="s">
+        <v>394</v>
+      </c>
+      <c r="P21" t="s">
+        <v>595</v>
+      </c>
+      <c r="Q21">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="H22" t="s">
+        <v>579</v>
+      </c>
+      <c r="I22">
+        <v>4.4376859485851716E-3</v>
+      </c>
+      <c r="N22" t="s">
+        <v>31</v>
+      </c>
+      <c r="O22" t="s">
+        <v>401</v>
+      </c>
+      <c r="P22" t="s">
+        <v>596</v>
+      </c>
+      <c r="Q22">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="H23" t="s">
+        <v>580</v>
+      </c>
+      <c r="I23">
+        <v>4.6185139610290856E-3</v>
+      </c>
+      <c r="N23" t="s">
+        <v>31</v>
+      </c>
+      <c r="O23" t="s">
+        <v>412</v>
+      </c>
+      <c r="P23" t="s">
+        <v>596</v>
+      </c>
+      <c r="Q23">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="H24" t="s">
+        <v>581</v>
+      </c>
+      <c r="I24">
+        <v>3.2985338023467049E-3</v>
+      </c>
+      <c r="N24" t="s">
+        <v>31</v>
+      </c>
+      <c r="O24" t="s">
+        <v>419</v>
+      </c>
+      <c r="P24" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q24">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="H25" t="s">
+        <v>582</v>
+      </c>
+      <c r="I25">
+        <v>6.1359066603704458E-3</v>
+      </c>
+      <c r="N25" t="s">
+        <v>31</v>
+      </c>
+      <c r="O25" t="s">
+        <v>429</v>
+      </c>
+      <c r="P25" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="H26" t="s">
+        <v>583</v>
+      </c>
+      <c r="I26">
+        <v>4.1747153711274333E-3</v>
+      </c>
+      <c r="N26" t="s">
+        <v>31</v>
+      </c>
+      <c r="O26" t="s">
+        <v>436</v>
+      </c>
+      <c r="P26" t="s">
+        <v>598</v>
+      </c>
+      <c r="Q26">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="H27" t="s">
+        <v>584</v>
+      </c>
+      <c r="I27">
+        <v>4.2211969618271396E-3</v>
+      </c>
+      <c r="N27" t="s">
+        <v>31</v>
+      </c>
+      <c r="O27" t="s">
+        <v>446</v>
+      </c>
+      <c r="P27" t="s">
+        <v>598</v>
+      </c>
+      <c r="Q27">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="H28" t="s">
+        <v>585</v>
+      </c>
+      <c r="I28">
+        <v>3.2826415366719228E-3</v>
+      </c>
+      <c r="N28" t="s">
+        <v>31</v>
+      </c>
+      <c r="O28" t="s">
+        <v>453</v>
+      </c>
+      <c r="P28" t="s">
+        <v>599</v>
+      </c>
+      <c r="Q28">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="N29" t="s">
+        <v>31</v>
+      </c>
+      <c r="O29" t="s">
+        <v>463</v>
+      </c>
+      <c r="P29" t="s">
+        <v>599</v>
+      </c>
+      <c r="Q29">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="N30" t="s">
+        <v>31</v>
+      </c>
+      <c r="O30" t="s">
+        <v>470</v>
+      </c>
+      <c r="P30" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q30">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="N31" t="s">
+        <v>31</v>
+      </c>
+      <c r="O31" t="s">
+        <v>480</v>
+      </c>
+      <c r="P31" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q31">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.45">
+      <c r="N32" t="s">
+        <v>31</v>
+      </c>
+      <c r="O32" t="s">
+        <v>487</v>
+      </c>
+      <c r="P32" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q32">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="33" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N33" t="s">
+        <v>31</v>
+      </c>
+      <c r="O33" t="s">
+        <v>497</v>
+      </c>
+      <c r="P33" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q33">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="34" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N34" t="s">
+        <v>31</v>
+      </c>
+      <c r="O34" t="s">
+        <v>602</v>
+      </c>
+      <c r="P34" t="s">
+        <v>601</v>
+      </c>
+      <c r="Q34">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="35" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N35" t="s">
+        <v>31</v>
+      </c>
+      <c r="O35" t="s">
+        <v>603</v>
+      </c>
+      <c r="P35" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q35">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="36" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N36" t="s">
+        <v>31</v>
+      </c>
+      <c r="O36" t="s">
+        <v>604</v>
+      </c>
+      <c r="P36" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q36">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="37" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N37" t="s">
+        <v>31</v>
+      </c>
+      <c r="O37" t="s">
+        <v>605</v>
+      </c>
+      <c r="P37" t="s">
+        <v>590</v>
+      </c>
+      <c r="Q37">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="38" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N38" t="s">
+        <v>31</v>
+      </c>
+      <c r="O38" t="s">
+        <v>606</v>
+      </c>
+      <c r="P38" t="s">
+        <v>595</v>
+      </c>
+      <c r="Q38">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="39" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N39" t="s">
+        <v>31</v>
+      </c>
+      <c r="O39" t="s">
+        <v>607</v>
+      </c>
+      <c r="P39" t="s">
+        <v>598</v>
+      </c>
+      <c r="Q39">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="40" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N40" t="s">
+        <v>31</v>
+      </c>
+      <c r="O40" t="s">
+        <v>608</v>
+      </c>
+      <c r="P40" t="s">
+        <v>591</v>
+      </c>
+      <c r="Q40">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="41" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N41" t="s">
+        <v>31</v>
+      </c>
+      <c r="O41" t="s">
+        <v>609</v>
+      </c>
+      <c r="P41" t="s">
+        <v>591</v>
+      </c>
+      <c r="Q41">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="42" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N42" t="s">
+        <v>31</v>
+      </c>
+      <c r="O42" t="s">
+        <v>610</v>
+      </c>
+      <c r="P42" t="s">
+        <v>599</v>
+      </c>
+      <c r="Q42">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="43" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N43" t="s">
+        <v>31</v>
+      </c>
+      <c r="O43" t="s">
+        <v>611</v>
+      </c>
+      <c r="P43" t="s">
+        <v>598</v>
+      </c>
+      <c r="Q43">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="44" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N44" t="s">
+        <v>31</v>
+      </c>
+      <c r="O44" t="s">
+        <v>612</v>
+      </c>
+      <c r="P44" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q44">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="45" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N45" t="s">
+        <v>31</v>
+      </c>
+      <c r="O45" t="s">
+        <v>613</v>
+      </c>
+      <c r="P45" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q45">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="46" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N46" t="s">
+        <v>31</v>
+      </c>
+      <c r="O46" t="s">
+        <v>614</v>
+      </c>
+      <c r="P46" t="s">
+        <v>598</v>
+      </c>
+      <c r="Q46">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="47" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N47" t="s">
+        <v>31</v>
+      </c>
+      <c r="O47" t="s">
+        <v>615</v>
+      </c>
+      <c r="P47" t="s">
+        <v>597</v>
+      </c>
+      <c r="Q47">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="48" spans="14:17" x14ac:dyDescent="0.45">
+      <c r="N48" t="s">
+        <v>31</v>
+      </c>
+      <c r="O48" t="s">
+        <v>616</v>
+      </c>
+      <c r="P48" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q48">
+        <v>0.95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF7B163-65F5-4C0A-A91D-AA146383F7A0}">
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="C1" t="s">
-        <v>543</v>
+        <v>617</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
@@ -22283,7 +23597,7 @@
         <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>544</v>
+        <v>618</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
@@ -22297,10 +23611,10 @@
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>545</v>
+        <v>619</v>
       </c>
       <c r="E4" t="s">
-        <v>546</v>
+        <v>620</v>
       </c>
       <c r="G4" t="s">
         <v>69</v>
@@ -22309,18 +23623,18 @@
         <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>545</v>
+        <v>619</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B5" t="s">
-        <v>548</v>
+        <v>622</v>
       </c>
       <c r="C5" t="s">
-        <v>549</v>
+        <v>623</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -22329,10 +23643,10 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>548</v>
+        <v>622</v>
       </c>
       <c r="H5" t="s">
-        <v>549</v>
+        <v>623</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -22340,13 +23654,13 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B6" t="s">
-        <v>550</v>
+        <v>624</v>
       </c>
       <c r="C6" t="s">
-        <v>551</v>
+        <v>625</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -22355,10 +23669,10 @@
         <v>2</v>
       </c>
       <c r="G6" t="s">
-        <v>550</v>
+        <v>624</v>
       </c>
       <c r="H6" t="s">
-        <v>551</v>
+        <v>625</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -22366,13 +23680,13 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B7" t="s">
-        <v>552</v>
+        <v>626</v>
       </c>
       <c r="C7" t="s">
-        <v>553</v>
+        <v>627</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -22381,10 +23695,10 @@
         <v>2</v>
       </c>
       <c r="G7" t="s">
-        <v>552</v>
+        <v>626</v>
       </c>
       <c r="H7" t="s">
-        <v>553</v>
+        <v>627</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -22392,13 +23706,13 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B8" t="s">
-        <v>554</v>
+        <v>628</v>
       </c>
       <c r="C8" t="s">
-        <v>555</v>
+        <v>629</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -22407,10 +23721,10 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>554</v>
+        <v>628</v>
       </c>
       <c r="H8" t="s">
-        <v>555</v>
+        <v>629</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -22418,13 +23732,13 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B9" t="s">
-        <v>556</v>
+        <v>630</v>
       </c>
       <c r="C9" t="s">
-        <v>557</v>
+        <v>631</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -22433,10 +23747,10 @@
         <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>556</v>
+        <v>630</v>
       </c>
       <c r="H9" t="s">
-        <v>557</v>
+        <v>631</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -22444,13 +23758,13 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B10" t="s">
-        <v>558</v>
+        <v>632</v>
       </c>
       <c r="C10" t="s">
-        <v>559</v>
+        <v>633</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -22459,10 +23773,10 @@
         <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>558</v>
+        <v>632</v>
       </c>
       <c r="H10" t="s">
-        <v>559</v>
+        <v>633</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -22470,13 +23784,13 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B11" t="s">
-        <v>560</v>
+        <v>634</v>
       </c>
       <c r="C11" t="s">
-        <v>561</v>
+        <v>635</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -22485,10 +23799,10 @@
         <v>2</v>
       </c>
       <c r="G11" t="s">
-        <v>560</v>
+        <v>634</v>
       </c>
       <c r="H11" t="s">
-        <v>561</v>
+        <v>635</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -22496,13 +23810,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B12" t="s">
-        <v>562</v>
+        <v>636</v>
       </c>
       <c r="C12" t="s">
-        <v>563</v>
+        <v>637</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -22511,10 +23825,10 @@
         <v>2</v>
       </c>
       <c r="G12" t="s">
-        <v>562</v>
+        <v>636</v>
       </c>
       <c r="H12" t="s">
-        <v>563</v>
+        <v>637</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -22522,13 +23836,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B13" t="s">
-        <v>564</v>
+        <v>638</v>
       </c>
       <c r="C13" t="s">
-        <v>565</v>
+        <v>639</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -22537,10 +23851,10 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>564</v>
+        <v>638</v>
       </c>
       <c r="H13" t="s">
-        <v>565</v>
+        <v>639</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -22548,13 +23862,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B14" t="s">
-        <v>566</v>
+        <v>640</v>
       </c>
       <c r="C14" t="s">
-        <v>567</v>
+        <v>641</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -22563,10 +23877,10 @@
         <v>2</v>
       </c>
       <c r="G14" t="s">
-        <v>566</v>
+        <v>640</v>
       </c>
       <c r="H14" t="s">
-        <v>567</v>
+        <v>641</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -22574,13 +23888,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B15" t="s">
-        <v>568</v>
+        <v>642</v>
       </c>
       <c r="C15" t="s">
-        <v>569</v>
+        <v>643</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -22589,10 +23903,10 @@
         <v>2</v>
       </c>
       <c r="G15" t="s">
-        <v>568</v>
+        <v>642</v>
       </c>
       <c r="H15" t="s">
-        <v>569</v>
+        <v>643</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -22600,13 +23914,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B16" t="s">
-        <v>570</v>
+        <v>644</v>
       </c>
       <c r="C16" t="s">
-        <v>571</v>
+        <v>645</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -22615,10 +23929,10 @@
         <v>2</v>
       </c>
       <c r="G16" t="s">
-        <v>570</v>
+        <v>644</v>
       </c>
       <c r="H16" t="s">
-        <v>571</v>
+        <v>645</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -22626,13 +23940,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B17" t="s">
-        <v>572</v>
+        <v>646</v>
       </c>
       <c r="C17" t="s">
-        <v>573</v>
+        <v>647</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -22641,10 +23955,10 @@
         <v>2</v>
       </c>
       <c r="G17" t="s">
-        <v>572</v>
+        <v>646</v>
       </c>
       <c r="H17" t="s">
-        <v>573</v>
+        <v>647</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -22652,13 +23966,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B18" t="s">
-        <v>574</v>
+        <v>648</v>
       </c>
       <c r="C18" t="s">
-        <v>575</v>
+        <v>649</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -22667,10 +23981,10 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
-        <v>574</v>
+        <v>648</v>
       </c>
       <c r="H18" t="s">
-        <v>575</v>
+        <v>649</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -22678,13 +23992,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B19" t="s">
-        <v>576</v>
+        <v>650</v>
       </c>
       <c r="C19" t="s">
-        <v>577</v>
+        <v>651</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -22693,10 +24007,10 @@
         <v>2</v>
       </c>
       <c r="G19" t="s">
-        <v>576</v>
+        <v>650</v>
       </c>
       <c r="H19" t="s">
-        <v>577</v>
+        <v>651</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -22704,13 +24018,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B20" t="s">
-        <v>578</v>
+        <v>652</v>
       </c>
       <c r="C20" t="s">
-        <v>579</v>
+        <v>653</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -22719,10 +24033,10 @@
         <v>2</v>
       </c>
       <c r="G20" t="s">
-        <v>578</v>
+        <v>652</v>
       </c>
       <c r="H20" t="s">
-        <v>579</v>
+        <v>653</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -22730,13 +24044,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B21" t="s">
-        <v>580</v>
+        <v>654</v>
       </c>
       <c r="C21" t="s">
-        <v>581</v>
+        <v>655</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -22745,10 +24059,10 @@
         <v>2</v>
       </c>
       <c r="G21" t="s">
-        <v>580</v>
+        <v>654</v>
       </c>
       <c r="H21" t="s">
-        <v>581</v>
+        <v>655</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -22756,13 +24070,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B22" t="s">
-        <v>582</v>
+        <v>656</v>
       </c>
       <c r="C22" t="s">
-        <v>583</v>
+        <v>657</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -22771,10 +24085,10 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>582</v>
+        <v>656</v>
       </c>
       <c r="H22" t="s">
-        <v>583</v>
+        <v>657</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -22782,13 +24096,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B23" t="s">
-        <v>584</v>
+        <v>658</v>
       </c>
       <c r="C23" t="s">
-        <v>585</v>
+        <v>659</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -22797,10 +24111,10 @@
         <v>2</v>
       </c>
       <c r="G23" t="s">
-        <v>584</v>
+        <v>658</v>
       </c>
       <c r="H23" t="s">
-        <v>585</v>
+        <v>659</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -22808,13 +24122,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B24" t="s">
-        <v>586</v>
+        <v>660</v>
       </c>
       <c r="C24" t="s">
-        <v>587</v>
+        <v>661</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -22823,10 +24137,10 @@
         <v>2</v>
       </c>
       <c r="G24" t="s">
-        <v>586</v>
+        <v>660</v>
       </c>
       <c r="H24" t="s">
-        <v>587</v>
+        <v>661</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -22834,13 +24148,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B25" t="s">
-        <v>588</v>
+        <v>662</v>
       </c>
       <c r="C25" t="s">
-        <v>589</v>
+        <v>663</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -22849,10 +24163,10 @@
         <v>2</v>
       </c>
       <c r="G25" t="s">
-        <v>588</v>
+        <v>662</v>
       </c>
       <c r="H25" t="s">
-        <v>589</v>
+        <v>663</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -22860,13 +24174,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B26" t="s">
-        <v>590</v>
+        <v>664</v>
       </c>
       <c r="C26" t="s">
-        <v>591</v>
+        <v>665</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -22875,10 +24189,10 @@
         <v>2</v>
       </c>
       <c r="G26" t="s">
-        <v>590</v>
+        <v>664</v>
       </c>
       <c r="H26" t="s">
-        <v>591</v>
+        <v>665</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -22886,13 +24200,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B27" t="s">
-        <v>592</v>
+        <v>666</v>
       </c>
       <c r="C27" t="s">
-        <v>593</v>
+        <v>667</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -22901,10 +24215,10 @@
         <v>2</v>
       </c>
       <c r="G27" t="s">
-        <v>592</v>
+        <v>666</v>
       </c>
       <c r="H27" t="s">
-        <v>593</v>
+        <v>667</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -22912,13 +24226,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B28" t="s">
-        <v>594</v>
+        <v>668</v>
       </c>
       <c r="C28" t="s">
-        <v>595</v>
+        <v>669</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -22927,10 +24241,10 @@
         <v>2</v>
       </c>
       <c r="G28" t="s">
-        <v>594</v>
+        <v>668</v>
       </c>
       <c r="H28" t="s">
-        <v>595</v>
+        <v>669</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -22938,13 +24252,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B29" t="s">
-        <v>596</v>
+        <v>670</v>
       </c>
       <c r="C29" t="s">
-        <v>597</v>
+        <v>671</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -22953,10 +24267,10 @@
         <v>2</v>
       </c>
       <c r="G29" t="s">
-        <v>596</v>
+        <v>670</v>
       </c>
       <c r="H29" t="s">
-        <v>597</v>
+        <v>671</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -22964,13 +24278,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B30" t="s">
-        <v>598</v>
+        <v>672</v>
       </c>
       <c r="C30" t="s">
-        <v>599</v>
+        <v>673</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -22979,10 +24293,10 @@
         <v>2</v>
       </c>
       <c r="G30" t="s">
-        <v>598</v>
+        <v>672</v>
       </c>
       <c r="H30" t="s">
-        <v>599</v>
+        <v>673</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -22990,13 +24304,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B31" t="s">
-        <v>600</v>
+        <v>674</v>
       </c>
       <c r="C31" t="s">
-        <v>601</v>
+        <v>675</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -23005,10 +24319,10 @@
         <v>2</v>
       </c>
       <c r="G31" t="s">
-        <v>600</v>
+        <v>674</v>
       </c>
       <c r="H31" t="s">
-        <v>601</v>
+        <v>675</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -23016,13 +24330,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>547</v>
+        <v>621</v>
       </c>
       <c r="B32" t="s">
-        <v>602</v>
+        <v>676</v>
       </c>
       <c r="C32" t="s">
-        <v>603</v>
+        <v>677</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -23031,12 +24345,298 @@
         <v>2</v>
       </c>
       <c r="G32" t="s">
-        <v>602</v>
+        <v>676</v>
       </c>
       <c r="H32" t="s">
-        <v>603</v>
+        <v>677</v>
       </c>
       <c r="I32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>621</v>
+      </c>
+      <c r="B33" t="s">
+        <v>678</v>
+      </c>
+      <c r="C33" t="s">
+        <v>679</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="G33" t="s">
+        <v>678</v>
+      </c>
+      <c r="H33" t="s">
+        <v>679</v>
+      </c>
+      <c r="I33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>621</v>
+      </c>
+      <c r="B34" t="s">
+        <v>680</v>
+      </c>
+      <c r="C34" t="s">
+        <v>681</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
+      </c>
+      <c r="G34" t="s">
+        <v>680</v>
+      </c>
+      <c r="H34" t="s">
+        <v>681</v>
+      </c>
+      <c r="I34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>621</v>
+      </c>
+      <c r="B35" t="s">
+        <v>682</v>
+      </c>
+      <c r="C35" t="s">
+        <v>683</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
+      </c>
+      <c r="G35" t="s">
+        <v>682</v>
+      </c>
+      <c r="H35" t="s">
+        <v>683</v>
+      </c>
+      <c r="I35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>621</v>
+      </c>
+      <c r="B36" t="s">
+        <v>684</v>
+      </c>
+      <c r="C36" t="s">
+        <v>685</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>2</v>
+      </c>
+      <c r="G36" t="s">
+        <v>684</v>
+      </c>
+      <c r="H36" t="s">
+        <v>685</v>
+      </c>
+      <c r="I36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>621</v>
+      </c>
+      <c r="B37" t="s">
+        <v>686</v>
+      </c>
+      <c r="C37" t="s">
+        <v>687</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>2</v>
+      </c>
+      <c r="G37" t="s">
+        <v>686</v>
+      </c>
+      <c r="H37" t="s">
+        <v>687</v>
+      </c>
+      <c r="I37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>621</v>
+      </c>
+      <c r="B38" t="s">
+        <v>688</v>
+      </c>
+      <c r="C38" t="s">
+        <v>689</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>2</v>
+      </c>
+      <c r="G38" t="s">
+        <v>688</v>
+      </c>
+      <c r="H38" t="s">
+        <v>689</v>
+      </c>
+      <c r="I38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>621</v>
+      </c>
+      <c r="B39" t="s">
+        <v>690</v>
+      </c>
+      <c r="C39" t="s">
+        <v>691</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>2</v>
+      </c>
+      <c r="G39" t="s">
+        <v>690</v>
+      </c>
+      <c r="H39" t="s">
+        <v>691</v>
+      </c>
+      <c r="I39">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>621</v>
+      </c>
+      <c r="B40" t="s">
+        <v>692</v>
+      </c>
+      <c r="C40" t="s">
+        <v>693</v>
+      </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="G40" t="s">
+        <v>692</v>
+      </c>
+      <c r="H40" t="s">
+        <v>693</v>
+      </c>
+      <c r="I40">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>621</v>
+      </c>
+      <c r="B41" t="s">
+        <v>694</v>
+      </c>
+      <c r="C41" t="s">
+        <v>695</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <v>2</v>
+      </c>
+      <c r="G41" t="s">
+        <v>694</v>
+      </c>
+      <c r="H41" t="s">
+        <v>695</v>
+      </c>
+      <c r="I41">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>621</v>
+      </c>
+      <c r="B42" t="s">
+        <v>696</v>
+      </c>
+      <c r="C42" t="s">
+        <v>697</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="G42" t="s">
+        <v>696</v>
+      </c>
+      <c r="H42" t="s">
+        <v>697</v>
+      </c>
+      <c r="I42">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>621</v>
+      </c>
+      <c r="B43" t="s">
+        <v>698</v>
+      </c>
+      <c r="C43" t="s">
+        <v>699</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="G43" t="s">
+        <v>698</v>
+      </c>
+      <c r="H43" t="s">
+        <v>699</v>
+      </c>
+      <c r="I43">
         <v>-1</v>
       </c>
     </row>

--- a/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_HRV_grids_kan10/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_HRV_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F471035F-E865-4511-AE2B-BCCDAD8D5A60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{84EA6D34-AD48-420D-BAAC-BB7D29B798DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1938,49 +1938,49 @@
     <t>co2_Kutina_HRV</t>
   </si>
   <si>
+    <t>ep_oil_gas_turbine_G100000400054-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_oil_gas_turbine_G100000410800-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_oil_combined_cycle_G100000400059-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_oil_steam_turbine_G100001031130_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_oil_combined_cycle_G100000400056-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400050-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_steam_turbine_G100000400055-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000400050-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000410800-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_combined_cycle_G100000400056-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_steam_turbine_G100001031130_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_combined_cycle_G100000400059-CHP_ccs-rf</t>
+    <t>ep_oil_combined_cycle_G100001031132-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400052-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_m_coal_subcritical_G100000108044_ccs-rf</t>
   </si>
   <si>
+    <t>ep_oil_gas_turbine_G100000400053-CHP_ccs-rf</t>
+  </si>
+  <si>
+    <t>ep_gas_combined_cycle_G100000400049-CHP_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_coal_subcritical_G100000108045_ccs-rf</t>
   </si>
   <si>
-    <t>ep_gas_combined_cycle_G100000400052-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_combined_cycle_G100001031132-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000400053-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_gas_combined_cycle_G100000400049-CHP_ccs-rf</t>
-  </si>
-  <si>
     <t>ep_oil_combined_cycle_G100000400058-CHP_ccs-rf</t>
   </si>
   <si>
     <t>ep_gas_combined_cycle_G100001031110-CHP_ccs-rf</t>
-  </si>
-  <si>
-    <t>ep_oil_gas_turbine_G100000400054-CHP_ccs-rf</t>
   </si>
   <si>
     <t>~UC_Sets: R_S: Allregions</t>
@@ -2721,7 +2721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64D78D1F-5518-46B2-8F4D-B435FE24898B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F6146BC-B5F8-480F-A1B7-D23F3AAE202B}">
   <dimension ref="B2:AG363"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10634,7 +10634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE83CD4B-EB9F-46B4-9394-C67172FA6ED9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE5B71AF-490F-4A0D-865A-F6F90ED82933}">
   <dimension ref="B9:L39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -22558,7 +22558,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94D3F4A-4BD8-49CA-8D9F-95DED6F64E25}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8463936F-F135-44EF-A3B0-D6E97BC83012}">
   <dimension ref="B2:Q48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -23375,7 +23375,7 @@
         <v>602</v>
       </c>
       <c r="P34" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="Q34">
         <v>0.95</v>
@@ -23389,7 +23389,7 @@
         <v>603</v>
       </c>
       <c r="P35" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="Q35">
         <v>0.95</v>
@@ -23403,7 +23403,7 @@
         <v>604</v>
       </c>
       <c r="P36" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="Q36">
         <v>0.95</v>
@@ -23417,7 +23417,7 @@
         <v>605</v>
       </c>
       <c r="P37" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="Q37">
         <v>0.95</v>
@@ -23431,7 +23431,7 @@
         <v>606</v>
       </c>
       <c r="P38" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="Q38">
         <v>0.95</v>
@@ -23445,7 +23445,7 @@
         <v>607</v>
       </c>
       <c r="P39" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="Q39">
         <v>0.95</v>
@@ -23459,10 +23459,10 @@
         <v>608</v>
       </c>
       <c r="P40" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="Q40">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="41" spans="14:17" x14ac:dyDescent="0.45">
@@ -23473,10 +23473,10 @@
         <v>609</v>
       </c>
       <c r="P41" t="s">
-        <v>591</v>
+        <v>598</v>
       </c>
       <c r="Q41">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="42" spans="14:17" x14ac:dyDescent="0.45">
@@ -23501,10 +23501,10 @@
         <v>611</v>
       </c>
       <c r="P43" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="Q43">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="44" spans="14:17" x14ac:dyDescent="0.45">
@@ -23543,10 +23543,10 @@
         <v>614</v>
       </c>
       <c r="P46" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="Q46">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="47" spans="14:17" x14ac:dyDescent="0.45">
@@ -23557,7 +23557,7 @@
         <v>615</v>
       </c>
       <c r="P47" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="Q47">
         <v>0.95</v>
@@ -23571,7 +23571,7 @@
         <v>616</v>
       </c>
       <c r="P48" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="Q48">
         <v>0.95</v>
@@ -23583,7 +23583,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF7B163-65F5-4C0A-A91D-AA146383F7A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CE5049C-779A-4F43-AE16-C9736EE7C8C0}">
   <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
